--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="21000" windowHeight="17055" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="616">
   <si>
     <t>int</t>
   </si>
@@ -1837,6 +1837,49 @@
   </si>
   <si>
     <t>删除成功</t>
+  </si>
+  <si>
+    <t>Text_Remaining</t>
+  </si>
+  <si>
+    <t>剩余:{0}天</t>
+  </si>
+  <si>
+    <t>Text_Vip1</t>
+  </si>
+  <si>
+    <t>广告播放失败，请重试</t>
+  </si>
+  <si>
+    <t>Text_Vip2</t>
+  </si>
+  <si>
+    <t>Vip购买</t>
+  </si>
+  <si>
+    <t>Text_Vip3</t>
+  </si>
+  <si>
+    <t>{0}天Vip
+Vip期间可免费保存所有服装</t>
+  </si>
+  <si>
+    <t>Text_Vip4</t>
+  </si>
+  <si>
+    <t>{0}派对币购买</t>
+  </si>
+  <si>
+    <t>Text_Vip5</t>
+  </si>
+  <si>
+    <t>看广告获得</t>
+  </si>
+  <si>
+    <t>Text_Vip6</t>
+  </si>
+  <si>
+    <t>购买Vip成功</t>
   </si>
 </sst>
 </file>
@@ -2503,11 +2546,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -10286,10 +10329,16 @@
       <c r="V235" s="3"/>
     </row>
     <row r="236" customHeight="1" spans="1:22">
-      <c r="A236" s="1"/>
-      <c r="B236" s="1"/>
+      <c r="A236" s="1">
+        <v>232</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>602</v>
+      </c>
       <c r="C236" s="3"/>
-      <c r="D236" s="3"/>
+      <c r="D236" s="3" t="s">
+        <v>603</v>
+      </c>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="G236" s="3"/>
@@ -10310,10 +10359,16 @@
       <c r="V236" s="3"/>
     </row>
     <row r="237" customHeight="1" spans="1:22">
-      <c r="A237" s="1"/>
-      <c r="B237" s="1"/>
+      <c r="A237" s="1">
+        <v>233</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>604</v>
+      </c>
       <c r="C237" s="3"/>
-      <c r="D237" s="6"/>
+      <c r="D237" s="6" t="s">
+        <v>605</v>
+      </c>
       <c r="E237" s="6"/>
       <c r="F237" s="6"/>
       <c r="G237" s="3"/>
@@ -10334,10 +10389,16 @@
       <c r="V237" s="3"/>
     </row>
     <row r="238" ht="18" customHeight="1" spans="1:22">
-      <c r="A238" s="1"/>
-      <c r="B238" s="1"/>
+      <c r="A238" s="1">
+        <v>234</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>606</v>
+      </c>
       <c r="C238" s="3"/>
-      <c r="D238" s="6"/>
+      <c r="D238" s="6" t="s">
+        <v>607</v>
+      </c>
       <c r="E238" s="6"/>
       <c r="F238" s="6"/>
       <c r="G238" s="3"/>
@@ -10358,10 +10419,16 @@
       <c r="V238" s="3"/>
     </row>
     <row r="239" ht="18" customHeight="1" spans="1:22">
-      <c r="A239" s="1"/>
-      <c r="B239" s="1"/>
+      <c r="A239" s="1">
+        <v>235</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>608</v>
+      </c>
       <c r="C239" s="3"/>
-      <c r="D239" s="6"/>
+      <c r="D239" s="7" t="s">
+        <v>609</v>
+      </c>
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
       <c r="G239" s="3"/>
@@ -10382,10 +10449,16 @@
       <c r="V239" s="3"/>
     </row>
     <row r="240" ht="18" customHeight="1" spans="1:22">
-      <c r="A240" s="1"/>
-      <c r="B240" s="1"/>
+      <c r="A240" s="1">
+        <v>236</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>610</v>
+      </c>
       <c r="C240" s="3"/>
-      <c r="D240" s="3"/>
+      <c r="D240" s="3" t="s">
+        <v>611</v>
+      </c>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
@@ -10406,10 +10479,16 @@
       <c r="V240" s="3"/>
     </row>
     <row r="241" ht="18" customHeight="1" spans="1:22">
-      <c r="A241" s="1"/>
-      <c r="B241" s="1"/>
+      <c r="A241" s="1">
+        <v>237</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>612</v>
+      </c>
       <c r="C241" s="3"/>
-      <c r="D241" s="3"/>
+      <c r="D241" s="3" t="s">
+        <v>613</v>
+      </c>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -10430,10 +10509,16 @@
       <c r="V241" s="3"/>
     </row>
     <row r="242" ht="18" customHeight="1" spans="1:22">
-      <c r="A242" s="1"/>
-      <c r="B242" s="1"/>
+      <c r="A242" s="1">
+        <v>238</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>614</v>
+      </c>
       <c r="C242" s="3"/>
-      <c r="D242" s="3"/>
+      <c r="D242" s="3" t="s">
+        <v>615</v>
+      </c>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
@@ -12619,7 +12704,7 @@
       <c r="C333" s="3"/>
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
-      <c r="F333" s="7"/>
+      <c r="F333" s="8"/>
       <c r="G333" s="3"/>
       <c r="H333" s="3"/>
       <c r="I333" s="3"/>
@@ -12643,7 +12728,7 @@
       <c r="C334" s="3"/>
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
-      <c r="F334" s="7"/>
+      <c r="F334" s="8"/>
       <c r="G334" s="3"/>
       <c r="H334" s="3"/>
       <c r="I334" s="3"/>
@@ -12667,7 +12752,7 @@
       <c r="C335" s="3"/>
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
-      <c r="F335" s="7"/>
+      <c r="F335" s="8"/>
       <c r="G335" s="3"/>
       <c r="H335" s="3"/>
       <c r="I335" s="3"/>
@@ -12691,7 +12776,7 @@
       <c r="C336" s="3"/>
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
-      <c r="F336" s="7"/>
+      <c r="F336" s="8"/>
       <c r="G336" s="3"/>
       <c r="H336" s="3"/>
       <c r="I336" s="3"/>
@@ -12715,7 +12800,7 @@
       <c r="C337" s="3"/>
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
-      <c r="F337" s="7"/>
+      <c r="F337" s="8"/>
       <c r="G337" s="3"/>
       <c r="H337" s="3"/>
       <c r="I337" s="3"/>
@@ -12739,7 +12824,7 @@
       <c r="C338" s="3"/>
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
-      <c r="F338" s="7"/>
+      <c r="F338" s="8"/>
       <c r="G338" s="3"/>
       <c r="H338" s="3"/>
       <c r="I338" s="3"/>
@@ -12763,7 +12848,7 @@
       <c r="C339" s="3"/>
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
-      <c r="F339" s="7"/>
+      <c r="F339" s="8"/>
       <c r="G339" s="3"/>
       <c r="H339" s="3"/>
       <c r="I339" s="3"/>
@@ -12787,7 +12872,7 @@
       <c r="C340" s="3"/>
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
-      <c r="F340" s="7"/>
+      <c r="F340" s="8"/>
       <c r="G340" s="3"/>
       <c r="H340" s="3"/>
       <c r="I340" s="3"/>
@@ -12811,7 +12896,7 @@
       <c r="C341" s="3"/>
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
-      <c r="F341" s="7"/>
+      <c r="F341" s="8"/>
       <c r="G341" s="3"/>
       <c r="H341" s="3"/>
       <c r="I341" s="3"/>
@@ -12835,7 +12920,7 @@
       <c r="C342" s="3"/>
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
-      <c r="F342" s="7"/>
+      <c r="F342" s="8"/>
       <c r="G342" s="3"/>
       <c r="H342" s="3"/>
       <c r="I342" s="3"/>
@@ -12979,7 +13064,7 @@
       <c r="C348" s="3"/>
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
-      <c r="F348" s="8"/>
+      <c r="F348" s="7"/>
       <c r="G348" s="3"/>
       <c r="H348" s="3"/>
       <c r="I348" s="3"/>

--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21240" windowHeight="17640"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="616">
   <si>
     <t>int</t>
   </si>
@@ -1837,6 +1837,49 @@
   </si>
   <si>
     <t>删除成功</t>
+  </si>
+  <si>
+    <t>Text_Remaining</t>
+  </si>
+  <si>
+    <t>剩余:{0}天</t>
+  </si>
+  <si>
+    <t>Text_Vip1</t>
+  </si>
+  <si>
+    <t>广告播放失败，请重试</t>
+  </si>
+  <si>
+    <t>Text_Vip2</t>
+  </si>
+  <si>
+    <t>Vip购买</t>
+  </si>
+  <si>
+    <t>Text_Vip3</t>
+  </si>
+  <si>
+    <t>{0}天Vip
+Vip期间可免费保存所有服装</t>
+  </si>
+  <si>
+    <t>Text_Vip4</t>
+  </si>
+  <si>
+    <t>{0}派对币购买</t>
+  </si>
+  <si>
+    <t>Text_Vip5</t>
+  </si>
+  <si>
+    <t>看广告获得</t>
+  </si>
+  <si>
+    <t>Text_Vip6</t>
+  </si>
+  <si>
+    <t>购买Vip成功</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1892,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1870,6 +1913,18 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2341,28 +2396,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2371,122 +2417,131 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2502,8 +2557,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2564,6 +2631,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00DEE0E3"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -10011,10 +10146,16 @@
       <c r="V235" s="3"/>
     </row>
     <row r="236" ht="17" customHeight="1" spans="1:22">
-      <c r="A236" s="1"/>
-      <c r="B236" s="1"/>
-      <c r="C236" s="3"/>
-      <c r="D236" s="3"/>
+      <c r="A236" s="1">
+        <v>232</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="C236" s="6"/>
+      <c r="D236" s="6" t="s">
+        <v>603</v>
+      </c>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="G236" s="3"/>
@@ -10035,12 +10176,18 @@
       <c r="V236" s="3"/>
     </row>
     <row r="237" ht="17" customHeight="1" spans="1:22">
-      <c r="A237" s="1"/>
-      <c r="B237" s="1"/>
-      <c r="C237" s="3"/>
-      <c r="D237" s="5"/>
-      <c r="E237" s="5"/>
-      <c r="F237" s="5"/>
+      <c r="A237" s="1">
+        <v>233</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="C237" s="6"/>
+      <c r="D237" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="E237" s="8"/>
+      <c r="F237" s="8"/>
       <c r="G237" s="3"/>
       <c r="H237" s="3"/>
       <c r="I237" s="3"/>
@@ -10059,12 +10206,18 @@
       <c r="V237" s="3"/>
     </row>
     <row r="238" ht="18" customHeight="1" spans="1:22">
-      <c r="A238" s="1"/>
-      <c r="B238" s="1"/>
-      <c r="C238" s="3"/>
-      <c r="D238" s="5"/>
-      <c r="E238" s="5"/>
-      <c r="F238" s="5"/>
+      <c r="A238" s="1">
+        <v>234</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="C238" s="6"/>
+      <c r="D238" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="E238" s="8"/>
+      <c r="F238" s="8"/>
       <c r="G238" s="3"/>
       <c r="H238" s="3"/>
       <c r="I238" s="3"/>
@@ -10083,12 +10236,18 @@
       <c r="V238" s="3"/>
     </row>
     <row r="239" ht="18" customHeight="1" spans="1:22">
-      <c r="A239" s="1"/>
-      <c r="B239" s="1"/>
-      <c r="C239" s="3"/>
-      <c r="D239" s="5"/>
-      <c r="E239" s="5"/>
-      <c r="F239" s="5"/>
+      <c r="A239" s="1">
+        <v>235</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="C239" s="6"/>
+      <c r="D239" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="E239" s="8"/>
+      <c r="F239" s="8"/>
       <c r="G239" s="3"/>
       <c r="H239" s="3"/>
       <c r="I239" s="3"/>
@@ -10107,10 +10266,16 @@
       <c r="V239" s="3"/>
     </row>
     <row r="240" ht="18" customHeight="1" spans="1:22">
-      <c r="A240" s="1"/>
-      <c r="B240" s="1"/>
-      <c r="C240" s="3"/>
-      <c r="D240" s="3"/>
+      <c r="A240" s="1">
+        <v>236</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="C240" s="6"/>
+      <c r="D240" s="6" t="s">
+        <v>611</v>
+      </c>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
@@ -10131,10 +10296,16 @@
       <c r="V240" s="3"/>
     </row>
     <row r="241" ht="18" customHeight="1" spans="1:22">
-      <c r="A241" s="1"/>
-      <c r="B241" s="1"/>
-      <c r="C241" s="3"/>
-      <c r="D241" s="3"/>
+      <c r="A241" s="1">
+        <v>237</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="C241" s="6"/>
+      <c r="D241" s="6" t="s">
+        <v>613</v>
+      </c>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -10155,10 +10326,16 @@
       <c r="V241" s="3"/>
     </row>
     <row r="242" ht="18" customHeight="1" spans="1:22">
-      <c r="A242" s="1"/>
-      <c r="B242" s="1"/>
-      <c r="C242" s="3"/>
-      <c r="D242" s="3"/>
+      <c r="A242" s="1">
+        <v>238</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="C242" s="6"/>
+      <c r="D242" s="6" t="s">
+        <v>615</v>
+      </c>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
@@ -10374,7 +10551,7 @@
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="3"/>
-      <c r="D251" s="5"/>
+      <c r="D251" s="8"/>
       <c r="E251" s="4"/>
       <c r="F251" s="4"/>
       <c r="G251" s="3"/>
@@ -10398,9 +10575,9 @@
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="3"/>
-      <c r="D252" s="5"/>
-      <c r="E252" s="5"/>
-      <c r="F252" s="5"/>
+      <c r="D252" s="8"/>
+      <c r="E252" s="8"/>
+      <c r="F252" s="8"/>
       <c r="G252" s="3"/>
       <c r="H252" s="3"/>
       <c r="I252" s="3"/>
@@ -10422,9 +10599,9 @@
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="3"/>
-      <c r="D253" s="5"/>
-      <c r="E253" s="5"/>
-      <c r="F253" s="5"/>
+      <c r="D253" s="8"/>
+      <c r="E253" s="8"/>
+      <c r="F253" s="8"/>
       <c r="G253" s="3"/>
       <c r="H253" s="3"/>
       <c r="I253" s="3"/>
@@ -10446,9 +10623,9 @@
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="3"/>
-      <c r="D254" s="5"/>
-      <c r="E254" s="5"/>
-      <c r="F254" s="5"/>
+      <c r="D254" s="8"/>
+      <c r="E254" s="8"/>
+      <c r="F254" s="8"/>
       <c r="G254" s="3"/>
       <c r="H254" s="3"/>
       <c r="I254" s="3"/>
@@ -12246,9 +12423,9 @@
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="3"/>
-      <c r="D329" s="5"/>
-      <c r="E329" s="5"/>
-      <c r="F329" s="5"/>
+      <c r="D329" s="8"/>
+      <c r="E329" s="8"/>
+      <c r="F329" s="8"/>
       <c r="G329" s="3"/>
       <c r="H329" s="3"/>
       <c r="I329" s="3"/>
@@ -12270,9 +12447,9 @@
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="3"/>
-      <c r="D330" s="5"/>
-      <c r="E330" s="5"/>
-      <c r="F330" s="5"/>
+      <c r="D330" s="8"/>
+      <c r="E330" s="8"/>
+      <c r="F330" s="8"/>
       <c r="G330" s="3"/>
       <c r="H330" s="3"/>
       <c r="I330" s="3"/>
@@ -12294,9 +12471,9 @@
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="3"/>
-      <c r="D331" s="5"/>
-      <c r="E331" s="5"/>
-      <c r="F331" s="5"/>
+      <c r="D331" s="8"/>
+      <c r="E331" s="8"/>
+      <c r="F331" s="8"/>
       <c r="G331" s="3"/>
       <c r="H331" s="3"/>
       <c r="I331" s="3"/>
@@ -12318,9 +12495,9 @@
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="3"/>
-      <c r="D332" s="5"/>
-      <c r="E332" s="5"/>
-      <c r="F332" s="5"/>
+      <c r="D332" s="8"/>
+      <c r="E332" s="8"/>
+      <c r="F332" s="8"/>
       <c r="G332" s="3"/>
       <c r="H332" s="3"/>
       <c r="I332" s="3"/>
@@ -12342,9 +12519,9 @@
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="3"/>
-      <c r="D333" s="5"/>
-      <c r="E333" s="5"/>
-      <c r="F333" s="6"/>
+      <c r="D333" s="8"/>
+      <c r="E333" s="8"/>
+      <c r="F333" s="10"/>
       <c r="G333" s="3"/>
       <c r="H333" s="3"/>
       <c r="I333" s="3"/>
@@ -12366,9 +12543,9 @@
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="3"/>
-      <c r="D334" s="5"/>
-      <c r="E334" s="5"/>
-      <c r="F334" s="6"/>
+      <c r="D334" s="8"/>
+      <c r="E334" s="8"/>
+      <c r="F334" s="10"/>
       <c r="G334" s="3"/>
       <c r="H334" s="3"/>
       <c r="I334" s="3"/>
@@ -12390,9 +12567,9 @@
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="3"/>
-      <c r="D335" s="5"/>
-      <c r="E335" s="5"/>
-      <c r="F335" s="6"/>
+      <c r="D335" s="8"/>
+      <c r="E335" s="8"/>
+      <c r="F335" s="10"/>
       <c r="G335" s="3"/>
       <c r="H335" s="3"/>
       <c r="I335" s="3"/>
@@ -12414,9 +12591,9 @@
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="3"/>
-      <c r="D336" s="5"/>
-      <c r="E336" s="5"/>
-      <c r="F336" s="6"/>
+      <c r="D336" s="8"/>
+      <c r="E336" s="8"/>
+      <c r="F336" s="10"/>
       <c r="G336" s="3"/>
       <c r="H336" s="3"/>
       <c r="I336" s="3"/>
@@ -12438,9 +12615,9 @@
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="3"/>
-      <c r="D337" s="5"/>
-      <c r="E337" s="5"/>
-      <c r="F337" s="6"/>
+      <c r="D337" s="8"/>
+      <c r="E337" s="8"/>
+      <c r="F337" s="10"/>
       <c r="G337" s="3"/>
       <c r="H337" s="3"/>
       <c r="I337" s="3"/>
@@ -12462,9 +12639,9 @@
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="3"/>
-      <c r="D338" s="5"/>
-      <c r="E338" s="5"/>
-      <c r="F338" s="6"/>
+      <c r="D338" s="8"/>
+      <c r="E338" s="8"/>
+      <c r="F338" s="10"/>
       <c r="G338" s="3"/>
       <c r="H338" s="3"/>
       <c r="I338" s="3"/>
@@ -12486,9 +12663,9 @@
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="3"/>
-      <c r="D339" s="5"/>
-      <c r="E339" s="5"/>
-      <c r="F339" s="6"/>
+      <c r="D339" s="8"/>
+      <c r="E339" s="8"/>
+      <c r="F339" s="10"/>
       <c r="G339" s="3"/>
       <c r="H339" s="3"/>
       <c r="I339" s="3"/>
@@ -12510,9 +12687,9 @@
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="3"/>
-      <c r="D340" s="5"/>
-      <c r="E340" s="5"/>
-      <c r="F340" s="6"/>
+      <c r="D340" s="8"/>
+      <c r="E340" s="8"/>
+      <c r="F340" s="10"/>
       <c r="G340" s="3"/>
       <c r="H340" s="3"/>
       <c r="I340" s="3"/>
@@ -12534,9 +12711,9 @@
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="3"/>
-      <c r="D341" s="5"/>
-      <c r="E341" s="5"/>
-      <c r="F341" s="6"/>
+      <c r="D341" s="8"/>
+      <c r="E341" s="8"/>
+      <c r="F341" s="10"/>
       <c r="G341" s="3"/>
       <c r="H341" s="3"/>
       <c r="I341" s="3"/>
@@ -12558,9 +12735,9 @@
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="3"/>
-      <c r="D342" s="5"/>
-      <c r="E342" s="5"/>
-      <c r="F342" s="6"/>
+      <c r="D342" s="8"/>
+      <c r="E342" s="8"/>
+      <c r="F342" s="10"/>
       <c r="G342" s="3"/>
       <c r="H342" s="3"/>
       <c r="I342" s="3"/>
@@ -12583,8 +12760,8 @@
       <c r="B343" s="1"/>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
-      <c r="E343" s="5"/>
-      <c r="F343" s="5"/>
+      <c r="E343" s="8"/>
+      <c r="F343" s="8"/>
       <c r="G343" s="3"/>
       <c r="H343" s="3"/>
       <c r="I343" s="3"/>
@@ -12607,8 +12784,8 @@
       <c r="B344" s="1"/>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
-      <c r="E344" s="5"/>
-      <c r="F344" s="5"/>
+      <c r="E344" s="8"/>
+      <c r="F344" s="8"/>
       <c r="G344" s="3"/>
       <c r="H344" s="3"/>
       <c r="I344" s="3"/>
@@ -12630,9 +12807,9 @@
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="3"/>
-      <c r="D345" s="5"/>
-      <c r="E345" s="5"/>
-      <c r="F345" s="5"/>
+      <c r="D345" s="8"/>
+      <c r="E345" s="8"/>
+      <c r="F345" s="8"/>
       <c r="G345" s="3"/>
       <c r="H345" s="3"/>
       <c r="I345" s="3"/>
@@ -12654,9 +12831,9 @@
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="3"/>
-      <c r="D346" s="5"/>
-      <c r="E346" s="5"/>
-      <c r="F346" s="5"/>
+      <c r="D346" s="8"/>
+      <c r="E346" s="8"/>
+      <c r="F346" s="8"/>
       <c r="G346" s="3"/>
       <c r="H346" s="3"/>
       <c r="I346" s="3"/>
@@ -12678,9 +12855,9 @@
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="3"/>
-      <c r="D347" s="5"/>
-      <c r="E347" s="5"/>
-      <c r="F347" s="5"/>
+      <c r="D347" s="8"/>
+      <c r="E347" s="8"/>
+      <c r="F347" s="8"/>
       <c r="G347" s="3"/>
       <c r="H347" s="3"/>
       <c r="I347" s="3"/>
@@ -12702,9 +12879,9 @@
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="3"/>
-      <c r="D348" s="5"/>
-      <c r="E348" s="5"/>
-      <c r="F348" s="7"/>
+      <c r="D348" s="8"/>
+      <c r="E348" s="8"/>
+      <c r="F348" s="11"/>
       <c r="G348" s="3"/>
       <c r="H348" s="3"/>
       <c r="I348" s="3"/>
@@ -12726,9 +12903,9 @@
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="3"/>
-      <c r="D349" s="5"/>
-      <c r="E349" s="5"/>
-      <c r="F349" s="5"/>
+      <c r="D349" s="8"/>
+      <c r="E349" s="8"/>
+      <c r="F349" s="8"/>
       <c r="G349" s="3"/>
       <c r="H349" s="3"/>
       <c r="I349" s="3"/>
@@ -12750,9 +12927,9 @@
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="3"/>
-      <c r="D350" s="5"/>
-      <c r="E350" s="5"/>
-      <c r="F350" s="5"/>
+      <c r="D350" s="8"/>
+      <c r="E350" s="8"/>
+      <c r="F350" s="8"/>
       <c r="G350" s="3"/>
       <c r="H350" s="3"/>
       <c r="I350" s="3"/>
@@ -12774,9 +12951,9 @@
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="3"/>
-      <c r="D351" s="5"/>
-      <c r="E351" s="5"/>
-      <c r="F351" s="5"/>
+      <c r="D351" s="8"/>
+      <c r="E351" s="8"/>
+      <c r="F351" s="8"/>
       <c r="G351" s="3"/>
       <c r="H351" s="3"/>
       <c r="I351" s="3"/>
@@ -12798,9 +12975,9 @@
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="3"/>
-      <c r="D352" s="5"/>
-      <c r="E352" s="5"/>
-      <c r="F352" s="5"/>
+      <c r="D352" s="8"/>
+      <c r="E352" s="8"/>
+      <c r="F352" s="8"/>
       <c r="G352" s="3"/>
       <c r="H352" s="3"/>
       <c r="I352" s="3"/>
@@ -12822,9 +12999,9 @@
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="3"/>
-      <c r="D353" s="5"/>
-      <c r="E353" s="5"/>
-      <c r="F353" s="5"/>
+      <c r="D353" s="8"/>
+      <c r="E353" s="8"/>
+      <c r="F353" s="8"/>
       <c r="G353" s="3"/>
       <c r="H353" s="3"/>
       <c r="I353" s="3"/>
@@ -12846,9 +13023,9 @@
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="3"/>
-      <c r="D354" s="5"/>
-      <c r="E354" s="5"/>
-      <c r="F354" s="5"/>
+      <c r="D354" s="8"/>
+      <c r="E354" s="8"/>
+      <c r="F354" s="8"/>
       <c r="G354" s="3"/>
       <c r="H354" s="3"/>
       <c r="I354" s="3"/>
@@ -12870,9 +13047,9 @@
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="3"/>
-      <c r="D355" s="5"/>
-      <c r="E355" s="5"/>
-      <c r="F355" s="5"/>
+      <c r="D355" s="8"/>
+      <c r="E355" s="8"/>
+      <c r="F355" s="8"/>
       <c r="G355" s="3"/>
       <c r="H355" s="3"/>
       <c r="I355" s="3"/>
@@ -12894,9 +13071,9 @@
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="3"/>
-      <c r="D356" s="5"/>
-      <c r="E356" s="5"/>
-      <c r="F356" s="5"/>
+      <c r="D356" s="8"/>
+      <c r="E356" s="8"/>
+      <c r="F356" s="8"/>
       <c r="G356" s="3"/>
       <c r="H356" s="3"/>
       <c r="I356" s="3"/>
@@ -12918,9 +13095,9 @@
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="3"/>
-      <c r="D357" s="5"/>
-      <c r="E357" s="5"/>
-      <c r="F357" s="5"/>
+      <c r="D357" s="8"/>
+      <c r="E357" s="8"/>
+      <c r="F357" s="8"/>
       <c r="G357" s="3"/>
       <c r="H357" s="3"/>
       <c r="I357" s="3"/>
@@ -12942,9 +13119,9 @@
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="3"/>
-      <c r="D358" s="5"/>
-      <c r="E358" s="5"/>
-      <c r="F358" s="5"/>
+      <c r="D358" s="8"/>
+      <c r="E358" s="8"/>
+      <c r="F358" s="8"/>
       <c r="G358" s="3"/>
       <c r="H358" s="3"/>
       <c r="I358" s="3"/>
@@ -12966,9 +13143,9 @@
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="3"/>
-      <c r="D359" s="5"/>
-      <c r="E359" s="5"/>
-      <c r="F359" s="5"/>
+      <c r="D359" s="8"/>
+      <c r="E359" s="8"/>
+      <c r="F359" s="8"/>
       <c r="G359" s="3"/>
       <c r="H359" s="3"/>
       <c r="I359" s="3"/>
@@ -12990,9 +13167,9 @@
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="3"/>
-      <c r="D360" s="5"/>
-      <c r="E360" s="5"/>
-      <c r="F360" s="5"/>
+      <c r="D360" s="8"/>
+      <c r="E360" s="8"/>
+      <c r="F360" s="8"/>
       <c r="G360" s="3"/>
       <c r="H360" s="3"/>
       <c r="I360" s="3"/>
@@ -13014,9 +13191,9 @@
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="3"/>
-      <c r="D361" s="5"/>
-      <c r="E361" s="5"/>
-      <c r="F361" s="5"/>
+      <c r="D361" s="8"/>
+      <c r="E361" s="8"/>
+      <c r="F361" s="8"/>
       <c r="G361" s="3"/>
       <c r="H361" s="3"/>
       <c r="I361" s="3"/>
@@ -13038,9 +13215,9 @@
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="3"/>
-      <c r="D362" s="5"/>
-      <c r="E362" s="5"/>
-      <c r="F362" s="5"/>
+      <c r="D362" s="8"/>
+      <c r="E362" s="8"/>
+      <c r="F362" s="8"/>
       <c r="G362" s="3"/>
       <c r="H362" s="3"/>
       <c r="I362" s="3"/>
@@ -13062,9 +13239,9 @@
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="3"/>
-      <c r="D363" s="5"/>
-      <c r="E363" s="5"/>
-      <c r="F363" s="5"/>
+      <c r="D363" s="8"/>
+      <c r="E363" s="8"/>
+      <c r="F363" s="8"/>
       <c r="G363" s="3"/>
       <c r="H363" s="3"/>
       <c r="I363" s="3"/>
@@ -13086,9 +13263,9 @@
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="3"/>
-      <c r="D364" s="5"/>
-      <c r="E364" s="5"/>
-      <c r="F364" s="5"/>
+      <c r="D364" s="8"/>
+      <c r="E364" s="8"/>
+      <c r="F364" s="8"/>
       <c r="G364" s="3"/>
       <c r="H364" s="3"/>
       <c r="I364" s="3"/>
@@ -13110,9 +13287,9 @@
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="3"/>
-      <c r="D365" s="5"/>
-      <c r="E365" s="5"/>
-      <c r="F365" s="5"/>
+      <c r="D365" s="8"/>
+      <c r="E365" s="8"/>
+      <c r="F365" s="8"/>
       <c r="G365" s="3"/>
       <c r="H365" s="3"/>
       <c r="I365" s="3"/>
@@ -13134,9 +13311,9 @@
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="3"/>
-      <c r="D366" s="5"/>
-      <c r="E366" s="5"/>
-      <c r="F366" s="5"/>
+      <c r="D366" s="8"/>
+      <c r="E366" s="8"/>
+      <c r="F366" s="8"/>
       <c r="G366" s="3"/>
       <c r="H366" s="3"/>
       <c r="I366" s="3"/>
@@ -13158,9 +13335,9 @@
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="3"/>
-      <c r="D367" s="5"/>
-      <c r="E367" s="5"/>
-      <c r="F367" s="5"/>
+      <c r="D367" s="8"/>
+      <c r="E367" s="8"/>
+      <c r="F367" s="8"/>
       <c r="G367" s="3"/>
       <c r="H367" s="3"/>
       <c r="I367" s="3"/>
@@ -13182,9 +13359,9 @@
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="3"/>
-      <c r="D368" s="5"/>
-      <c r="E368" s="5"/>
-      <c r="F368" s="5"/>
+      <c r="D368" s="8"/>
+      <c r="E368" s="8"/>
+      <c r="F368" s="8"/>
       <c r="G368" s="3"/>
       <c r="H368" s="3"/>
       <c r="I368" s="3"/>
@@ -13206,9 +13383,9 @@
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="3"/>
-      <c r="D369" s="5"/>
-      <c r="E369" s="5"/>
-      <c r="F369" s="5"/>
+      <c r="D369" s="8"/>
+      <c r="E369" s="8"/>
+      <c r="F369" s="8"/>
       <c r="G369" s="3"/>
       <c r="H369" s="3"/>
       <c r="I369" s="3"/>
@@ -13230,9 +13407,9 @@
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="3"/>
-      <c r="D370" s="5"/>
-      <c r="E370" s="5"/>
-      <c r="F370" s="5"/>
+      <c r="D370" s="8"/>
+      <c r="E370" s="8"/>
+      <c r="F370" s="8"/>
       <c r="G370" s="3"/>
       <c r="H370" s="3"/>
       <c r="I370" s="3"/>
@@ -13254,9 +13431,9 @@
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="3"/>
-      <c r="D371" s="5"/>
-      <c r="E371" s="5"/>
-      <c r="F371" s="5"/>
+      <c r="D371" s="8"/>
+      <c r="E371" s="8"/>
+      <c r="F371" s="8"/>
       <c r="G371" s="3"/>
       <c r="H371" s="3"/>
       <c r="I371" s="3"/>
@@ -13278,9 +13455,9 @@
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="3"/>
-      <c r="D372" s="5"/>
-      <c r="E372" s="5"/>
-      <c r="F372" s="5"/>
+      <c r="D372" s="8"/>
+      <c r="E372" s="8"/>
+      <c r="F372" s="8"/>
       <c r="G372" s="3"/>
       <c r="H372" s="3"/>
       <c r="I372" s="3"/>
@@ -13302,9 +13479,9 @@
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="3"/>
-      <c r="D373" s="5"/>
-      <c r="E373" s="5"/>
-      <c r="F373" s="5"/>
+      <c r="D373" s="8"/>
+      <c r="E373" s="8"/>
+      <c r="F373" s="8"/>
       <c r="G373" s="3"/>
       <c r="H373" s="3"/>
       <c r="I373" s="3"/>
@@ -13326,9 +13503,9 @@
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="3"/>
-      <c r="D374" s="5"/>
-      <c r="E374" s="5"/>
-      <c r="F374" s="5"/>
+      <c r="D374" s="8"/>
+      <c r="E374" s="8"/>
+      <c r="F374" s="8"/>
       <c r="G374" s="3"/>
       <c r="H374" s="3"/>
       <c r="I374" s="3"/>
@@ -13350,9 +13527,9 @@
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="3"/>
-      <c r="D375" s="5"/>
-      <c r="E375" s="5"/>
-      <c r="F375" s="5"/>
+      <c r="D375" s="8"/>
+      <c r="E375" s="8"/>
+      <c r="F375" s="8"/>
       <c r="G375" s="3"/>
       <c r="H375" s="3"/>
       <c r="I375" s="3"/>
@@ -13375,7 +13552,7 @@
       <c r="B376" s="1"/>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
-      <c r="E376" s="5"/>
+      <c r="E376" s="8"/>
       <c r="F376" s="3"/>
       <c r="G376" s="3"/>
       <c r="H376" s="3"/>
@@ -13399,7 +13576,7 @@
       <c r="B377" s="1"/>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
-      <c r="E377" s="5"/>
+      <c r="E377" s="8"/>
       <c r="F377" s="3"/>
       <c r="G377" s="3"/>
       <c r="H377" s="3"/>
@@ -13423,7 +13600,7 @@
       <c r="B378" s="1"/>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
-      <c r="E378" s="5"/>
+      <c r="E378" s="8"/>
       <c r="F378" s="3"/>
       <c r="G378" s="3"/>
       <c r="H378" s="3"/>
@@ -13447,7 +13624,7 @@
       <c r="B379" s="1"/>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
-      <c r="E379" s="5"/>
+      <c r="E379" s="8"/>
       <c r="F379" s="3"/>
       <c r="G379" s="3"/>
       <c r="H379" s="3"/>
@@ -13471,7 +13648,7 @@
       <c r="B380" s="1"/>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
-      <c r="E380" s="5"/>
+      <c r="E380" s="8"/>
       <c r="F380" s="3"/>
       <c r="G380" s="3"/>
       <c r="H380" s="3"/>
@@ -13495,7 +13672,7 @@
       <c r="B381" s="1"/>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
-      <c r="E381" s="5"/>
+      <c r="E381" s="8"/>
       <c r="F381" s="3"/>
       <c r="G381" s="3"/>
       <c r="H381" s="3"/>
@@ -13519,7 +13696,7 @@
       <c r="B382" s="1"/>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
-      <c r="E382" s="5"/>
+      <c r="E382" s="8"/>
       <c r="F382" s="3"/>
       <c r="G382" s="3"/>
       <c r="H382" s="3"/>
@@ -13542,9 +13719,9 @@
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="3"/>
-      <c r="D383" s="5"/>
-      <c r="E383" s="5"/>
-      <c r="F383" s="5"/>
+      <c r="D383" s="8"/>
+      <c r="E383" s="8"/>
+      <c r="F383" s="8"/>
       <c r="G383" s="3"/>
       <c r="H383" s="3"/>
       <c r="I383" s="3"/>
@@ -13566,9 +13743,9 @@
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="3"/>
-      <c r="D384" s="5"/>
-      <c r="E384" s="5"/>
-      <c r="F384" s="5"/>
+      <c r="D384" s="8"/>
+      <c r="E384" s="8"/>
+      <c r="F384" s="8"/>
       <c r="G384" s="3"/>
       <c r="H384" s="3"/>
       <c r="I384" s="3"/>
@@ -13588,9 +13765,9 @@
     </row>
     <row r="385" spans="3:22">
       <c r="C385" s="3"/>
-      <c r="D385" s="5"/>
-      <c r="E385" s="5"/>
-      <c r="F385" s="5"/>
+      <c r="D385" s="8"/>
+      <c r="E385" s="8"/>
+      <c r="F385" s="8"/>
       <c r="G385" s="3"/>
       <c r="H385" s="3"/>
       <c r="I385" s="3"/>
@@ -13610,9 +13787,9 @@
     </row>
     <row r="386" spans="3:22">
       <c r="C386" s="3"/>
-      <c r="D386" s="5"/>
-      <c r="E386" s="5"/>
-      <c r="F386" s="5"/>
+      <c r="D386" s="8"/>
+      <c r="E386" s="8"/>
+      <c r="F386" s="8"/>
       <c r="G386" s="3"/>
       <c r="H386" s="3"/>
       <c r="I386" s="3"/>
@@ -13632,9 +13809,9 @@
     </row>
     <row r="387" spans="3:22">
       <c r="C387" s="3"/>
-      <c r="D387" s="5"/>
-      <c r="E387" s="5"/>
-      <c r="F387" s="5"/>
+      <c r="D387" s="8"/>
+      <c r="E387" s="8"/>
+      <c r="F387" s="8"/>
       <c r="G387" s="3"/>
       <c r="H387" s="3"/>
       <c r="I387" s="3"/>
@@ -13654,9 +13831,9 @@
     </row>
     <row r="388" spans="3:22">
       <c r="C388" s="3"/>
-      <c r="D388" s="5"/>
-      <c r="E388" s="5"/>
-      <c r="F388" s="5"/>
+      <c r="D388" s="8"/>
+      <c r="E388" s="8"/>
+      <c r="F388" s="8"/>
       <c r="G388" s="3"/>
       <c r="H388" s="3"/>
       <c r="I388" s="3"/>
@@ -13676,9 +13853,9 @@
     </row>
     <row r="389" spans="3:22">
       <c r="C389" s="3"/>
-      <c r="D389" s="5"/>
-      <c r="E389" s="5"/>
-      <c r="F389" s="5"/>
+      <c r="D389" s="8"/>
+      <c r="E389" s="8"/>
+      <c r="F389" s="8"/>
       <c r="G389" s="3"/>
       <c r="H389" s="3"/>
       <c r="I389" s="3"/>
@@ -13698,9 +13875,9 @@
     </row>
     <row r="390" spans="3:22">
       <c r="C390" s="3"/>
-      <c r="D390" s="5"/>
-      <c r="E390" s="5"/>
-      <c r="F390" s="5"/>
+      <c r="D390" s="8"/>
+      <c r="E390" s="8"/>
+      <c r="F390" s="8"/>
       <c r="G390" s="3"/>
       <c r="H390" s="3"/>
       <c r="I390" s="3"/>
@@ -13720,9 +13897,9 @@
     </row>
     <row r="391" spans="3:22">
       <c r="C391" s="3"/>
-      <c r="D391" s="5"/>
-      <c r="E391" s="5"/>
-      <c r="F391" s="5"/>
+      <c r="D391" s="8"/>
+      <c r="E391" s="8"/>
+      <c r="F391" s="8"/>
       <c r="G391" s="3"/>
       <c r="H391" s="3"/>
       <c r="I391" s="3"/>
@@ -13742,9 +13919,9 @@
     </row>
     <row r="392" spans="3:22">
       <c r="C392" s="3"/>
-      <c r="D392" s="5"/>
-      <c r="E392" s="5"/>
-      <c r="F392" s="5"/>
+      <c r="D392" s="8"/>
+      <c r="E392" s="8"/>
+      <c r="F392" s="8"/>
       <c r="G392" s="3"/>
       <c r="H392" s="3"/>
       <c r="I392" s="3"/>
@@ -13764,9 +13941,9 @@
     </row>
     <row r="393" spans="3:22">
       <c r="C393" s="3"/>
-      <c r="D393" s="5"/>
-      <c r="E393" s="5"/>
-      <c r="F393" s="5"/>
+      <c r="D393" s="8"/>
+      <c r="E393" s="8"/>
+      <c r="F393" s="8"/>
       <c r="G393" s="3"/>
       <c r="H393" s="3"/>
       <c r="I393" s="3"/>
@@ -13786,9 +13963,9 @@
     </row>
     <row r="394" spans="3:22">
       <c r="C394" s="3"/>
-      <c r="D394" s="5"/>
-      <c r="E394" s="5"/>
-      <c r="F394" s="5"/>
+      <c r="D394" s="8"/>
+      <c r="E394" s="8"/>
+      <c r="F394" s="8"/>
       <c r="G394" s="3"/>
       <c r="H394" s="3"/>
       <c r="I394" s="3"/>
@@ -13808,9 +13985,9 @@
     </row>
     <row r="395" spans="3:22">
       <c r="C395" s="3"/>
-      <c r="D395" s="5"/>
-      <c r="E395" s="5"/>
-      <c r="F395" s="5"/>
+      <c r="D395" s="8"/>
+      <c r="E395" s="8"/>
+      <c r="F395" s="8"/>
       <c r="G395" s="3"/>
       <c r="H395" s="3"/>
       <c r="I395" s="3"/>
@@ -13830,9 +14007,9 @@
     </row>
     <row r="396" spans="3:22">
       <c r="C396" s="3"/>
-      <c r="D396" s="5"/>
-      <c r="E396" s="5"/>
-      <c r="F396" s="5"/>
+      <c r="D396" s="8"/>
+      <c r="E396" s="8"/>
+      <c r="F396" s="8"/>
       <c r="G396" s="3"/>
       <c r="H396" s="3"/>
       <c r="I396" s="3"/>
@@ -13852,9 +14029,9 @@
     </row>
     <row r="397" spans="3:22">
       <c r="C397" s="3"/>
-      <c r="D397" s="5"/>
-      <c r="E397" s="5"/>
-      <c r="F397" s="5"/>
+      <c r="D397" s="8"/>
+      <c r="E397" s="8"/>
+      <c r="F397" s="8"/>
       <c r="G397" s="3"/>
       <c r="H397" s="3"/>
       <c r="I397" s="3"/>
@@ -13874,9 +14051,9 @@
     </row>
     <row r="398" spans="3:22">
       <c r="C398" s="3"/>
-      <c r="D398" s="5"/>
-      <c r="E398" s="5"/>
-      <c r="F398" s="5"/>
+      <c r="D398" s="8"/>
+      <c r="E398" s="8"/>
+      <c r="F398" s="8"/>
       <c r="G398" s="3"/>
       <c r="H398" s="3"/>
       <c r="I398" s="3"/>
@@ -13896,9 +14073,9 @@
     </row>
     <row r="399" spans="3:22">
       <c r="C399" s="3"/>
-      <c r="D399" s="5"/>
-      <c r="E399" s="5"/>
-      <c r="F399" s="5"/>
+      <c r="D399" s="8"/>
+      <c r="E399" s="8"/>
+      <c r="F399" s="8"/>
       <c r="G399" s="3"/>
       <c r="H399" s="3"/>
       <c r="I399" s="3"/>
@@ -13918,9 +14095,9 @@
     </row>
     <row r="400" spans="3:22">
       <c r="C400" s="3"/>
-      <c r="D400" s="5"/>
-      <c r="E400" s="5"/>
-      <c r="F400" s="5"/>
+      <c r="D400" s="8"/>
+      <c r="E400" s="8"/>
+      <c r="F400" s="8"/>
       <c r="G400" s="3"/>
       <c r="H400" s="3"/>
       <c r="I400" s="3"/>
@@ -13940,9 +14117,9 @@
     </row>
     <row r="401" spans="3:22">
       <c r="C401" s="3"/>
-      <c r="D401" s="5"/>
-      <c r="E401" s="5"/>
-      <c r="F401" s="5"/>
+      <c r="D401" s="8"/>
+      <c r="E401" s="8"/>
+      <c r="F401" s="8"/>
       <c r="G401" s="3"/>
       <c r="H401" s="3"/>
       <c r="I401" s="3"/>
@@ -13962,9 +14139,9 @@
     </row>
     <row r="402" spans="3:22">
       <c r="C402" s="3"/>
-      <c r="D402" s="5"/>
-      <c r="E402" s="5"/>
-      <c r="F402" s="5"/>
+      <c r="D402" s="8"/>
+      <c r="E402" s="8"/>
+      <c r="F402" s="8"/>
       <c r="G402" s="3"/>
       <c r="H402" s="3"/>
       <c r="I402" s="3"/>
@@ -13984,9 +14161,9 @@
     </row>
     <row r="403" spans="3:22">
       <c r="C403" s="3"/>
-      <c r="D403" s="5"/>
-      <c r="E403" s="5"/>
-      <c r="F403" s="5"/>
+      <c r="D403" s="8"/>
+      <c r="E403" s="8"/>
+      <c r="F403" s="8"/>
       <c r="G403" s="3"/>
       <c r="H403" s="3"/>
       <c r="I403" s="3"/>
@@ -14006,9 +14183,9 @@
     </row>
     <row r="404" spans="3:22">
       <c r="C404" s="3"/>
-      <c r="D404" s="5"/>
-      <c r="E404" s="5"/>
-      <c r="F404" s="5"/>
+      <c r="D404" s="8"/>
+      <c r="E404" s="8"/>
+      <c r="F404" s="8"/>
       <c r="G404" s="3"/>
       <c r="H404" s="3"/>
       <c r="I404" s="3"/>
@@ -14028,9 +14205,9 @@
     </row>
     <row r="405" spans="3:22">
       <c r="C405" s="3"/>
-      <c r="D405" s="5"/>
-      <c r="E405" s="5"/>
-      <c r="F405" s="5"/>
+      <c r="D405" s="8"/>
+      <c r="E405" s="8"/>
+      <c r="F405" s="8"/>
       <c r="G405" s="3"/>
       <c r="H405" s="3"/>
       <c r="I405" s="3"/>
@@ -14050,9 +14227,9 @@
     </row>
     <row r="406" spans="3:22">
       <c r="C406" s="3"/>
-      <c r="D406" s="5"/>
-      <c r="E406" s="5"/>
-      <c r="F406" s="5"/>
+      <c r="D406" s="8"/>
+      <c r="E406" s="8"/>
+      <c r="F406" s="8"/>
       <c r="G406" s="3"/>
       <c r="H406" s="3"/>
       <c r="I406" s="3"/>
@@ -14072,9 +14249,9 @@
     </row>
     <row r="407" spans="3:22">
       <c r="C407" s="3"/>
-      <c r="D407" s="5"/>
-      <c r="E407" s="5"/>
-      <c r="F407" s="5"/>
+      <c r="D407" s="8"/>
+      <c r="E407" s="8"/>
+      <c r="F407" s="8"/>
       <c r="G407" s="3"/>
       <c r="H407" s="3"/>
       <c r="I407" s="3"/>
@@ -14094,9 +14271,9 @@
     </row>
     <row r="408" spans="3:22">
       <c r="C408" s="3"/>
-      <c r="D408" s="5"/>
-      <c r="E408" s="5"/>
-      <c r="F408" s="5"/>
+      <c r="D408" s="8"/>
+      <c r="E408" s="8"/>
+      <c r="F408" s="8"/>
       <c r="G408" s="3"/>
       <c r="H408" s="3"/>
       <c r="I408" s="3"/>
@@ -14116,9 +14293,9 @@
     </row>
     <row r="409" spans="3:22">
       <c r="C409" s="3"/>
-      <c r="D409" s="5"/>
-      <c r="E409" s="5"/>
-      <c r="F409" s="5"/>
+      <c r="D409" s="8"/>
+      <c r="E409" s="8"/>
+      <c r="F409" s="8"/>
       <c r="G409" s="3"/>
       <c r="H409" s="3"/>
       <c r="I409" s="3"/>
@@ -14138,9 +14315,9 @@
     </row>
     <row r="410" spans="3:22">
       <c r="C410" s="3"/>
-      <c r="D410" s="5"/>
-      <c r="E410" s="5"/>
-      <c r="F410" s="5"/>
+      <c r="D410" s="8"/>
+      <c r="E410" s="8"/>
+      <c r="F410" s="8"/>
       <c r="G410" s="3"/>
       <c r="H410" s="3"/>
       <c r="I410" s="3"/>
@@ -14160,9 +14337,9 @@
     </row>
     <row r="411" spans="3:22">
       <c r="C411" s="3"/>
-      <c r="D411" s="5"/>
-      <c r="E411" s="5"/>
-      <c r="F411" s="5"/>
+      <c r="D411" s="8"/>
+      <c r="E411" s="8"/>
+      <c r="F411" s="8"/>
       <c r="G411" s="3"/>
       <c r="H411" s="3"/>
       <c r="I411" s="3"/>
@@ -14182,9 +14359,9 @@
     </row>
     <row r="412" spans="3:22">
       <c r="C412" s="3"/>
-      <c r="D412" s="5"/>
-      <c r="E412" s="5"/>
-      <c r="F412" s="5"/>
+      <c r="D412" s="8"/>
+      <c r="E412" s="8"/>
+      <c r="F412" s="8"/>
       <c r="G412" s="3"/>
       <c r="H412" s="3"/>
       <c r="I412" s="3"/>
@@ -14204,9 +14381,9 @@
     </row>
     <row r="413" spans="3:22">
       <c r="C413" s="3"/>
-      <c r="D413" s="5"/>
-      <c r="E413" s="5"/>
-      <c r="F413" s="5"/>
+      <c r="D413" s="8"/>
+      <c r="E413" s="8"/>
+      <c r="F413" s="8"/>
       <c r="G413" s="3"/>
       <c r="H413" s="3"/>
       <c r="I413" s="3"/>
@@ -14226,9 +14403,9 @@
     </row>
     <row r="414" spans="3:22">
       <c r="C414" s="3"/>
-      <c r="D414" s="5"/>
-      <c r="E414" s="5"/>
-      <c r="F414" s="5"/>
+      <c r="D414" s="8"/>
+      <c r="E414" s="8"/>
+      <c r="F414" s="8"/>
       <c r="G414" s="3"/>
       <c r="H414" s="3"/>
       <c r="I414" s="3"/>
@@ -14248,9 +14425,9 @@
     </row>
     <row r="415" spans="3:22">
       <c r="C415" s="3"/>
-      <c r="D415" s="5"/>
-      <c r="E415" s="5"/>
-      <c r="F415" s="5"/>
+      <c r="D415" s="8"/>
+      <c r="E415" s="8"/>
+      <c r="F415" s="8"/>
       <c r="G415" s="3"/>
       <c r="H415" s="3"/>
       <c r="I415" s="3"/>
@@ -14270,9 +14447,9 @@
     </row>
     <row r="416" spans="3:22">
       <c r="C416" s="3"/>
-      <c r="D416" s="5"/>
-      <c r="E416" s="5"/>
-      <c r="F416" s="5"/>
+      <c r="D416" s="8"/>
+      <c r="E416" s="8"/>
+      <c r="F416" s="8"/>
       <c r="G416" s="3"/>
       <c r="H416" s="3"/>
       <c r="I416" s="3"/>
@@ -14292,9 +14469,9 @@
     </row>
     <row r="417" spans="3:22">
       <c r="C417" s="3"/>
-      <c r="D417" s="5"/>
-      <c r="E417" s="5"/>
-      <c r="F417" s="5"/>
+      <c r="D417" s="8"/>
+      <c r="E417" s="8"/>
+      <c r="F417" s="8"/>
       <c r="G417" s="3"/>
       <c r="H417" s="3"/>
       <c r="I417" s="3"/>
@@ -14314,9 +14491,9 @@
     </row>
     <row r="418" spans="3:22">
       <c r="C418" s="3"/>
-      <c r="D418" s="5"/>
-      <c r="E418" s="5"/>
-      <c r="F418" s="5"/>
+      <c r="D418" s="8"/>
+      <c r="E418" s="8"/>
+      <c r="F418" s="8"/>
       <c r="G418" s="3"/>
       <c r="H418" s="3"/>
       <c r="I418" s="3"/>
@@ -14336,9 +14513,9 @@
     </row>
     <row r="419" spans="3:22">
       <c r="C419" s="3"/>
-      <c r="D419" s="5"/>
-      <c r="E419" s="5"/>
-      <c r="F419" s="5"/>
+      <c r="D419" s="8"/>
+      <c r="E419" s="8"/>
+      <c r="F419" s="8"/>
       <c r="G419" s="3"/>
       <c r="H419" s="3"/>
       <c r="I419" s="3"/>
@@ -14358,9 +14535,9 @@
     </row>
     <row r="420" spans="3:22">
       <c r="C420" s="3"/>
-      <c r="D420" s="5"/>
-      <c r="E420" s="5"/>
-      <c r="F420" s="5"/>
+      <c r="D420" s="8"/>
+      <c r="E420" s="8"/>
+      <c r="F420" s="8"/>
       <c r="G420" s="3"/>
       <c r="H420" s="3"/>
       <c r="I420" s="3"/>
@@ -14380,9 +14557,9 @@
     </row>
     <row r="421" spans="3:22">
       <c r="C421" s="3"/>
-      <c r="D421" s="5"/>
-      <c r="E421" s="5"/>
-      <c r="F421" s="5"/>
+      <c r="D421" s="8"/>
+      <c r="E421" s="8"/>
+      <c r="F421" s="8"/>
       <c r="G421" s="3"/>
       <c r="H421" s="3"/>
       <c r="I421" s="3"/>
@@ -14402,9 +14579,9 @@
     </row>
     <row r="422" spans="3:22">
       <c r="C422" s="3"/>
-      <c r="D422" s="5"/>
-      <c r="E422" s="5"/>
-      <c r="F422" s="5"/>
+      <c r="D422" s="8"/>
+      <c r="E422" s="8"/>
+      <c r="F422" s="8"/>
       <c r="G422" s="3"/>
       <c r="H422" s="3"/>
       <c r="I422" s="3"/>
@@ -14424,9 +14601,9 @@
     </row>
     <row r="423" spans="3:22">
       <c r="C423" s="3"/>
-      <c r="D423" s="5"/>
-      <c r="E423" s="5"/>
-      <c r="F423" s="5"/>
+      <c r="D423" s="8"/>
+      <c r="E423" s="8"/>
+      <c r="F423" s="8"/>
       <c r="G423" s="3"/>
       <c r="H423" s="3"/>
       <c r="I423" s="3"/>
@@ -14446,9 +14623,9 @@
     </row>
     <row r="424" spans="3:22">
       <c r="C424" s="3"/>
-      <c r="D424" s="5"/>
-      <c r="E424" s="5"/>
-      <c r="F424" s="5"/>
+      <c r="D424" s="8"/>
+      <c r="E424" s="8"/>
+      <c r="F424" s="8"/>
       <c r="G424" s="3"/>
       <c r="H424" s="3"/>
       <c r="I424" s="3"/>
@@ -14468,9 +14645,9 @@
     </row>
     <row r="425" spans="3:22">
       <c r="C425" s="3"/>
-      <c r="D425" s="5"/>
-      <c r="E425" s="5"/>
-      <c r="F425" s="5"/>
+      <c r="D425" s="8"/>
+      <c r="E425" s="8"/>
+      <c r="F425" s="8"/>
       <c r="G425" s="3"/>
       <c r="H425" s="3"/>
       <c r="I425" s="3"/>
@@ -14490,9 +14667,9 @@
     </row>
     <row r="426" spans="3:22">
       <c r="C426" s="3"/>
-      <c r="D426" s="5"/>
-      <c r="E426" s="5"/>
-      <c r="F426" s="5"/>
+      <c r="D426" s="8"/>
+      <c r="E426" s="8"/>
+      <c r="F426" s="8"/>
       <c r="G426" s="3"/>
       <c r="H426" s="3"/>
       <c r="I426" s="3"/>
@@ -14512,9 +14689,9 @@
     </row>
     <row r="427" spans="3:22">
       <c r="C427" s="3"/>
-      <c r="D427" s="5"/>
-      <c r="E427" s="5"/>
-      <c r="F427" s="5"/>
+      <c r="D427" s="8"/>
+      <c r="E427" s="8"/>
+      <c r="F427" s="8"/>
       <c r="G427" s="3"/>
       <c r="H427" s="3"/>
       <c r="I427" s="3"/>
@@ -14534,9 +14711,9 @@
     </row>
     <row r="428" spans="3:22">
       <c r="C428" s="3"/>
-      <c r="D428" s="5"/>
-      <c r="E428" s="5"/>
-      <c r="F428" s="5"/>
+      <c r="D428" s="8"/>
+      <c r="E428" s="8"/>
+      <c r="F428" s="8"/>
       <c r="G428" s="3"/>
       <c r="H428" s="3"/>
       <c r="I428" s="3"/>
@@ -14556,9 +14733,9 @@
     </row>
     <row r="429" spans="3:22">
       <c r="C429" s="3"/>
-      <c r="D429" s="5"/>
-      <c r="E429" s="5"/>
-      <c r="F429" s="5"/>
+      <c r="D429" s="8"/>
+      <c r="E429" s="8"/>
+      <c r="F429" s="8"/>
       <c r="G429" s="3"/>
       <c r="H429" s="3"/>
       <c r="I429" s="3"/>
@@ -14578,9 +14755,9 @@
     </row>
     <row r="430" spans="3:22">
       <c r="C430" s="3"/>
-      <c r="D430" s="5"/>
-      <c r="E430" s="5"/>
-      <c r="F430" s="5"/>
+      <c r="D430" s="8"/>
+      <c r="E430" s="8"/>
+      <c r="F430" s="8"/>
       <c r="G430" s="3"/>
       <c r="H430" s="3"/>
       <c r="I430" s="3"/>
@@ -14600,9 +14777,9 @@
     </row>
     <row r="431" spans="3:22">
       <c r="C431" s="3"/>
-      <c r="D431" s="5"/>
-      <c r="E431" s="5"/>
-      <c r="F431" s="5"/>
+      <c r="D431" s="8"/>
+      <c r="E431" s="8"/>
+      <c r="F431" s="8"/>
       <c r="G431" s="3"/>
       <c r="H431" s="3"/>
       <c r="I431" s="3"/>
@@ -14622,9 +14799,9 @@
     </row>
     <row r="432" spans="3:22">
       <c r="C432" s="3"/>
-      <c r="D432" s="5"/>
-      <c r="E432" s="5"/>
-      <c r="F432" s="5"/>
+      <c r="D432" s="8"/>
+      <c r="E432" s="8"/>
+      <c r="F432" s="8"/>
       <c r="G432" s="3"/>
       <c r="H432" s="3"/>
       <c r="I432" s="3"/>
@@ -14644,9 +14821,9 @@
     </row>
     <row r="433" spans="3:22">
       <c r="C433" s="3"/>
-      <c r="D433" s="5"/>
-      <c r="E433" s="5"/>
-      <c r="F433" s="5"/>
+      <c r="D433" s="8"/>
+      <c r="E433" s="8"/>
+      <c r="F433" s="8"/>
       <c r="G433" s="3"/>
       <c r="H433" s="3"/>
       <c r="I433" s="3"/>
@@ -14666,9 +14843,9 @@
     </row>
     <row r="434" spans="3:22">
       <c r="C434" s="3"/>
-      <c r="D434" s="5"/>
-      <c r="E434" s="5"/>
-      <c r="F434" s="5"/>
+      <c r="D434" s="8"/>
+      <c r="E434" s="8"/>
+      <c r="F434" s="8"/>
       <c r="G434" s="3"/>
       <c r="H434" s="3"/>
       <c r="I434" s="3"/>
@@ -14688,9 +14865,9 @@
     </row>
     <row r="435" spans="3:22">
       <c r="C435" s="3"/>
-      <c r="D435" s="5"/>
-      <c r="E435" s="5"/>
-      <c r="F435" s="5"/>
+      <c r="D435" s="8"/>
+      <c r="E435" s="8"/>
+      <c r="F435" s="8"/>
       <c r="G435" s="3"/>
       <c r="H435" s="3"/>
       <c r="I435" s="3"/>
@@ -14710,9 +14887,9 @@
     </row>
     <row r="436" spans="3:22">
       <c r="C436" s="3"/>
-      <c r="D436" s="5"/>
-      <c r="E436" s="5"/>
-      <c r="F436" s="5"/>
+      <c r="D436" s="8"/>
+      <c r="E436" s="8"/>
+      <c r="F436" s="8"/>
       <c r="G436" s="3"/>
       <c r="H436" s="3"/>
       <c r="I436" s="3"/>
@@ -14732,9 +14909,9 @@
     </row>
     <row r="437" spans="3:22">
       <c r="C437" s="3"/>
-      <c r="D437" s="5"/>
-      <c r="E437" s="5"/>
-      <c r="F437" s="5"/>
+      <c r="D437" s="8"/>
+      <c r="E437" s="8"/>
+      <c r="F437" s="8"/>
       <c r="G437" s="3"/>
       <c r="H437" s="3"/>
       <c r="I437" s="3"/>
@@ -14754,9 +14931,9 @@
     </row>
     <row r="438" spans="3:22">
       <c r="C438" s="3"/>
-      <c r="D438" s="5"/>
-      <c r="E438" s="5"/>
-      <c r="F438" s="5"/>
+      <c r="D438" s="8"/>
+      <c r="E438" s="8"/>
+      <c r="F438" s="8"/>
       <c r="G438" s="3"/>
       <c r="H438" s="3"/>
       <c r="I438" s="3"/>
@@ -14776,9 +14953,9 @@
     </row>
     <row r="439" spans="3:22">
       <c r="C439" s="3"/>
-      <c r="D439" s="5"/>
-      <c r="E439" s="5"/>
-      <c r="F439" s="5"/>
+      <c r="D439" s="8"/>
+      <c r="E439" s="8"/>
+      <c r="F439" s="8"/>
       <c r="G439" s="3"/>
       <c r="H439" s="3"/>
       <c r="I439" s="3"/>
@@ -14798,9 +14975,9 @@
     </row>
     <row r="440" spans="3:22">
       <c r="C440" s="3"/>
-      <c r="D440" s="5"/>
-      <c r="E440" s="5"/>
-      <c r="F440" s="5"/>
+      <c r="D440" s="8"/>
+      <c r="E440" s="8"/>
+      <c r="F440" s="8"/>
       <c r="G440" s="3"/>
       <c r="H440" s="3"/>
       <c r="I440" s="3"/>
@@ -14820,9 +14997,9 @@
     </row>
     <row r="441" spans="3:22">
       <c r="C441" s="3"/>
-      <c r="D441" s="5"/>
-      <c r="E441" s="5"/>
-      <c r="F441" s="5"/>
+      <c r="D441" s="8"/>
+      <c r="E441" s="8"/>
+      <c r="F441" s="8"/>
       <c r="G441" s="3"/>
       <c r="H441" s="3"/>
       <c r="I441" s="3"/>
@@ -14842,9 +15019,9 @@
     </row>
     <row r="442" spans="3:22">
       <c r="C442" s="3"/>
-      <c r="D442" s="5"/>
-      <c r="E442" s="5"/>
-      <c r="F442" s="5"/>
+      <c r="D442" s="8"/>
+      <c r="E442" s="8"/>
+      <c r="F442" s="8"/>
       <c r="G442" s="3"/>
       <c r="H442" s="3"/>
       <c r="I442" s="3"/>
@@ -14864,9 +15041,9 @@
     </row>
     <row r="443" spans="3:22">
       <c r="C443" s="3"/>
-      <c r="D443" s="5"/>
-      <c r="E443" s="5"/>
-      <c r="F443" s="5"/>
+      <c r="D443" s="8"/>
+      <c r="E443" s="8"/>
+      <c r="F443" s="8"/>
       <c r="G443" s="3"/>
       <c r="H443" s="3"/>
       <c r="I443" s="3"/>
@@ -14886,9 +15063,9 @@
     </row>
     <row r="444" spans="3:22">
       <c r="C444" s="3"/>
-      <c r="D444" s="5"/>
-      <c r="E444" s="5"/>
-      <c r="F444" s="5"/>
+      <c r="D444" s="8"/>
+      <c r="E444" s="8"/>
+      <c r="F444" s="8"/>
       <c r="G444" s="3"/>
       <c r="H444" s="3"/>
       <c r="I444" s="3"/>
@@ -14908,9 +15085,9 @@
     </row>
     <row r="445" spans="3:22">
       <c r="C445" s="3"/>
-      <c r="D445" s="5"/>
-      <c r="E445" s="5"/>
-      <c r="F445" s="5"/>
+      <c r="D445" s="8"/>
+      <c r="E445" s="8"/>
+      <c r="F445" s="8"/>
       <c r="G445" s="3"/>
       <c r="H445" s="3"/>
       <c r="I445" s="3"/>
@@ -14930,9 +15107,9 @@
     </row>
     <row r="446" spans="3:22">
       <c r="C446" s="3"/>
-      <c r="D446" s="5"/>
-      <c r="E446" s="5"/>
-      <c r="F446" s="5"/>
+      <c r="D446" s="8"/>
+      <c r="E446" s="8"/>
+      <c r="F446" s="8"/>
       <c r="G446" s="3"/>
       <c r="H446" s="3"/>
       <c r="I446" s="3"/>
@@ -14952,9 +15129,9 @@
     </row>
     <row r="447" spans="3:22">
       <c r="C447" s="3"/>
-      <c r="D447" s="5"/>
-      <c r="E447" s="5"/>
-      <c r="F447" s="5"/>
+      <c r="D447" s="8"/>
+      <c r="E447" s="8"/>
+      <c r="F447" s="8"/>
       <c r="G447" s="3"/>
       <c r="H447" s="3"/>
       <c r="I447" s="3"/>
@@ -14974,9 +15151,9 @@
     </row>
     <row r="448" spans="3:22">
       <c r="C448" s="3"/>
-      <c r="D448" s="5"/>
-      <c r="E448" s="5"/>
-      <c r="F448" s="5"/>
+      <c r="D448" s="8"/>
+      <c r="E448" s="8"/>
+      <c r="F448" s="8"/>
       <c r="G448" s="3"/>
       <c r="H448" s="3"/>
       <c r="I448" s="3"/>
@@ -14996,9 +15173,9 @@
     </row>
     <row r="449" spans="3:22">
       <c r="C449" s="3"/>
-      <c r="D449" s="5"/>
-      <c r="E449" s="5"/>
-      <c r="F449" s="5"/>
+      <c r="D449" s="8"/>
+      <c r="E449" s="8"/>
+      <c r="F449" s="8"/>
       <c r="G449" s="3"/>
       <c r="H449" s="3"/>
       <c r="I449" s="3"/>
@@ -15018,9 +15195,9 @@
     </row>
     <row r="450" spans="3:22">
       <c r="C450" s="3"/>
-      <c r="D450" s="5"/>
-      <c r="E450" s="5"/>
-      <c r="F450" s="5"/>
+      <c r="D450" s="8"/>
+      <c r="E450" s="8"/>
+      <c r="F450" s="8"/>
       <c r="G450" s="3"/>
       <c r="H450" s="3"/>
       <c r="I450" s="3"/>
@@ -15040,9 +15217,9 @@
     </row>
     <row r="451" spans="3:22">
       <c r="C451" s="3"/>
-      <c r="D451" s="5"/>
-      <c r="E451" s="5"/>
-      <c r="F451" s="5"/>
+      <c r="D451" s="8"/>
+      <c r="E451" s="8"/>
+      <c r="F451" s="8"/>
       <c r="G451" s="3"/>
       <c r="H451" s="3"/>
       <c r="I451" s="3"/>
@@ -15062,9 +15239,9 @@
     </row>
     <row r="452" spans="3:22">
       <c r="C452" s="3"/>
-      <c r="D452" s="5"/>
-      <c r="E452" s="5"/>
-      <c r="F452" s="5"/>
+      <c r="D452" s="8"/>
+      <c r="E452" s="8"/>
+      <c r="F452" s="8"/>
       <c r="G452" s="3"/>
       <c r="H452" s="3"/>
       <c r="I452" s="3"/>
@@ -15084,9 +15261,9 @@
     </row>
     <row r="453" spans="3:22">
       <c r="C453" s="3"/>
-      <c r="D453" s="5"/>
-      <c r="E453" s="5"/>
-      <c r="F453" s="5"/>
+      <c r="D453" s="8"/>
+      <c r="E453" s="8"/>
+      <c r="F453" s="8"/>
       <c r="G453" s="3"/>
       <c r="H453" s="3"/>
       <c r="I453" s="3"/>
@@ -15106,9 +15283,9 @@
     </row>
     <row r="454" spans="3:22">
       <c r="C454" s="3"/>
-      <c r="D454" s="5"/>
-      <c r="E454" s="5"/>
-      <c r="F454" s="5"/>
+      <c r="D454" s="8"/>
+      <c r="E454" s="8"/>
+      <c r="F454" s="8"/>
       <c r="G454" s="3"/>
       <c r="H454" s="3"/>
       <c r="I454" s="3"/>
@@ -15128,9 +15305,9 @@
     </row>
     <row r="455" spans="3:22">
       <c r="C455" s="3"/>
-      <c r="D455" s="5"/>
-      <c r="E455" s="5"/>
-      <c r="F455" s="5"/>
+      <c r="D455" s="8"/>
+      <c r="E455" s="8"/>
+      <c r="F455" s="8"/>
       <c r="G455" s="3"/>
       <c r="H455" s="3"/>
       <c r="I455" s="3"/>
@@ -15150,9 +15327,9 @@
     </row>
     <row r="456" spans="3:22">
       <c r="C456" s="3"/>
-      <c r="D456" s="5"/>
-      <c r="E456" s="5"/>
-      <c r="F456" s="5"/>
+      <c r="D456" s="8"/>
+      <c r="E456" s="8"/>
+      <c r="F456" s="8"/>
       <c r="G456" s="3"/>
       <c r="H456" s="3"/>
       <c r="I456" s="3"/>
@@ -15172,9 +15349,9 @@
     </row>
     <row r="457" spans="3:22">
       <c r="C457" s="3"/>
-      <c r="D457" s="5"/>
-      <c r="E457" s="5"/>
-      <c r="F457" s="5"/>
+      <c r="D457" s="8"/>
+      <c r="E457" s="8"/>
+      <c r="F457" s="8"/>
       <c r="G457" s="3"/>
       <c r="H457" s="3"/>
       <c r="I457" s="3"/>
@@ -15194,9 +15371,9 @@
     </row>
     <row r="458" spans="3:22">
       <c r="C458" s="3"/>
-      <c r="D458" s="5"/>
-      <c r="E458" s="5"/>
-      <c r="F458" s="5"/>
+      <c r="D458" s="8"/>
+      <c r="E458" s="8"/>
+      <c r="F458" s="8"/>
       <c r="G458" s="3"/>
       <c r="H458" s="3"/>
       <c r="I458" s="3"/>
@@ -15216,9 +15393,9 @@
     </row>
     <row r="459" spans="3:22">
       <c r="C459" s="3"/>
-      <c r="D459" s="5"/>
-      <c r="E459" s="5"/>
-      <c r="F459" s="5"/>
+      <c r="D459" s="8"/>
+      <c r="E459" s="8"/>
+      <c r="F459" s="8"/>
       <c r="G459" s="3"/>
       <c r="H459" s="3"/>
       <c r="I459" s="3"/>
@@ -15238,9 +15415,9 @@
     </row>
     <row r="460" spans="3:22">
       <c r="C460" s="3"/>
-      <c r="D460" s="5"/>
-      <c r="E460" s="5"/>
-      <c r="F460" s="5"/>
+      <c r="D460" s="8"/>
+      <c r="E460" s="8"/>
+      <c r="F460" s="8"/>
       <c r="G460" s="3"/>
       <c r="H460" s="3"/>
       <c r="I460" s="3"/>
@@ -15260,9 +15437,9 @@
     </row>
     <row r="461" spans="3:22">
       <c r="C461" s="3"/>
-      <c r="D461" s="5"/>
-      <c r="E461" s="5"/>
-      <c r="F461" s="5"/>
+      <c r="D461" s="8"/>
+      <c r="E461" s="8"/>
+      <c r="F461" s="8"/>
       <c r="G461" s="3"/>
       <c r="H461" s="3"/>
       <c r="I461" s="3"/>
@@ -15282,9 +15459,9 @@
     </row>
     <row r="462" spans="3:22">
       <c r="C462" s="3"/>
-      <c r="D462" s="5"/>
-      <c r="E462" s="5"/>
-      <c r="F462" s="5"/>
+      <c r="D462" s="8"/>
+      <c r="E462" s="8"/>
+      <c r="F462" s="8"/>
       <c r="G462" s="3"/>
       <c r="H462" s="3"/>
       <c r="I462" s="3"/>
@@ -15304,9 +15481,9 @@
     </row>
     <row r="463" spans="3:22">
       <c r="C463" s="3"/>
-      <c r="D463" s="5"/>
-      <c r="E463" s="5"/>
-      <c r="F463" s="5"/>
+      <c r="D463" s="8"/>
+      <c r="E463" s="8"/>
+      <c r="F463" s="8"/>
       <c r="G463" s="3"/>
       <c r="H463" s="3"/>
       <c r="I463" s="3"/>
@@ -15326,9 +15503,9 @@
     </row>
     <row r="464" spans="3:22">
       <c r="C464" s="3"/>
-      <c r="D464" s="5"/>
-      <c r="E464" s="5"/>
-      <c r="F464" s="5"/>
+      <c r="D464" s="8"/>
+      <c r="E464" s="8"/>
+      <c r="F464" s="8"/>
       <c r="G464" s="3"/>
       <c r="H464" s="3"/>
       <c r="I464" s="3"/>
@@ -15348,9 +15525,9 @@
     </row>
     <row r="465" spans="3:22">
       <c r="C465" s="3"/>
-      <c r="D465" s="5"/>
-      <c r="E465" s="5"/>
-      <c r="F465" s="5"/>
+      <c r="D465" s="8"/>
+      <c r="E465" s="8"/>
+      <c r="F465" s="8"/>
       <c r="G465" s="3"/>
       <c r="H465" s="3"/>
       <c r="I465" s="3"/>
@@ -15370,9 +15547,9 @@
     </row>
     <row r="466" spans="3:22">
       <c r="C466" s="3"/>
-      <c r="D466" s="5"/>
-      <c r="E466" s="5"/>
-      <c r="F466" s="5"/>
+      <c r="D466" s="8"/>
+      <c r="E466" s="8"/>
+      <c r="F466" s="8"/>
       <c r="G466" s="3"/>
       <c r="H466" s="3"/>
       <c r="I466" s="3"/>
@@ -15392,9 +15569,9 @@
     </row>
     <row r="467" spans="3:22">
       <c r="C467" s="3"/>
-      <c r="D467" s="5"/>
-      <c r="E467" s="5"/>
-      <c r="F467" s="5"/>
+      <c r="D467" s="8"/>
+      <c r="E467" s="8"/>
+      <c r="F467" s="8"/>
       <c r="G467" s="3"/>
       <c r="H467" s="3"/>
       <c r="I467" s="3"/>
@@ -15414,9 +15591,9 @@
     </row>
     <row r="468" spans="3:22">
       <c r="C468" s="3"/>
-      <c r="D468" s="5"/>
-      <c r="E468" s="5"/>
-      <c r="F468" s="5"/>
+      <c r="D468" s="8"/>
+      <c r="E468" s="8"/>
+      <c r="F468" s="8"/>
       <c r="G468" s="3"/>
       <c r="H468" s="3"/>
       <c r="I468" s="3"/>
@@ -15436,9 +15613,9 @@
     </row>
     <row r="469" spans="3:22">
       <c r="C469" s="3"/>
-      <c r="D469" s="5"/>
-      <c r="E469" s="5"/>
-      <c r="F469" s="5"/>
+      <c r="D469" s="8"/>
+      <c r="E469" s="8"/>
+      <c r="F469" s="8"/>
       <c r="G469" s="3"/>
       <c r="H469" s="3"/>
       <c r="I469" s="3"/>
@@ -15458,9 +15635,9 @@
     </row>
     <row r="470" spans="3:22">
       <c r="C470" s="3"/>
-      <c r="D470" s="5"/>
-      <c r="E470" s="5"/>
-      <c r="F470" s="5"/>
+      <c r="D470" s="8"/>
+      <c r="E470" s="8"/>
+      <c r="F470" s="8"/>
       <c r="G470" s="3"/>
       <c r="H470" s="3"/>
       <c r="I470" s="3"/>
@@ -15480,9 +15657,9 @@
     </row>
     <row r="471" spans="3:22">
       <c r="C471" s="3"/>
-      <c r="D471" s="5"/>
-      <c r="E471" s="5"/>
-      <c r="F471" s="5"/>
+      <c r="D471" s="8"/>
+      <c r="E471" s="8"/>
+      <c r="F471" s="8"/>
       <c r="G471" s="3"/>
       <c r="H471" s="3"/>
       <c r="I471" s="3"/>
@@ -15502,9 +15679,9 @@
     </row>
     <row r="472" spans="3:22">
       <c r="C472" s="3"/>
-      <c r="D472" s="5"/>
-      <c r="E472" s="5"/>
-      <c r="F472" s="5"/>
+      <c r="D472" s="8"/>
+      <c r="E472" s="8"/>
+      <c r="F472" s="8"/>
       <c r="G472" s="3"/>
       <c r="H472" s="3"/>
       <c r="I472" s="3"/>
@@ -15524,9 +15701,9 @@
     </row>
     <row r="473" spans="3:22">
       <c r="C473" s="3"/>
-      <c r="D473" s="5"/>
-      <c r="E473" s="5"/>
-      <c r="F473" s="5"/>
+      <c r="D473" s="8"/>
+      <c r="E473" s="8"/>
+      <c r="F473" s="8"/>
       <c r="G473" s="3"/>
       <c r="H473" s="3"/>
       <c r="I473" s="3"/>
@@ -15546,9 +15723,9 @@
     </row>
     <row r="474" spans="3:22">
       <c r="C474" s="3"/>
-      <c r="D474" s="5"/>
-      <c r="E474" s="5"/>
-      <c r="F474" s="5"/>
+      <c r="D474" s="8"/>
+      <c r="E474" s="8"/>
+      <c r="F474" s="8"/>
       <c r="G474" s="3"/>
       <c r="H474" s="3"/>
       <c r="I474" s="3"/>
@@ -15568,9 +15745,9 @@
     </row>
     <row r="475" spans="3:22">
       <c r="C475" s="3"/>
-      <c r="D475" s="5"/>
-      <c r="E475" s="5"/>
-      <c r="F475" s="5"/>
+      <c r="D475" s="8"/>
+      <c r="E475" s="8"/>
+      <c r="F475" s="8"/>
       <c r="G475" s="3"/>
       <c r="H475" s="3"/>
       <c r="I475" s="3"/>
@@ -15590,9 +15767,9 @@
     </row>
     <row r="476" spans="3:22">
       <c r="C476" s="3"/>
-      <c r="D476" s="5"/>
-      <c r="E476" s="5"/>
-      <c r="F476" s="5"/>
+      <c r="D476" s="8"/>
+      <c r="E476" s="8"/>
+      <c r="F476" s="8"/>
       <c r="G476" s="3"/>
       <c r="H476" s="3"/>
       <c r="I476" s="3"/>
@@ -15612,9 +15789,9 @@
     </row>
     <row r="477" spans="3:22">
       <c r="C477" s="3"/>
-      <c r="D477" s="5"/>
-      <c r="E477" s="5"/>
-      <c r="F477" s="5"/>
+      <c r="D477" s="8"/>
+      <c r="E477" s="8"/>
+      <c r="F477" s="8"/>
       <c r="G477" s="3"/>
       <c r="H477" s="3"/>
       <c r="I477" s="3"/>
@@ -15634,9 +15811,9 @@
     </row>
     <row r="478" spans="3:22">
       <c r="C478" s="3"/>
-      <c r="D478" s="5"/>
-      <c r="E478" s="5"/>
-      <c r="F478" s="5"/>
+      <c r="D478" s="8"/>
+      <c r="E478" s="8"/>
+      <c r="F478" s="8"/>
       <c r="G478" s="3"/>
       <c r="H478" s="3"/>
       <c r="I478" s="3"/>
@@ -15656,9 +15833,9 @@
     </row>
     <row r="479" spans="3:22">
       <c r="C479" s="3"/>
-      <c r="D479" s="5"/>
-      <c r="E479" s="5"/>
-      <c r="F479" s="5"/>
+      <c r="D479" s="8"/>
+      <c r="E479" s="8"/>
+      <c r="F479" s="8"/>
       <c r="G479" s="3"/>
       <c r="H479" s="3"/>
       <c r="I479" s="3"/>
@@ -15678,9 +15855,9 @@
     </row>
     <row r="480" spans="3:22">
       <c r="C480" s="3"/>
-      <c r="D480" s="5"/>
-      <c r="E480" s="5"/>
-      <c r="F480" s="5"/>
+      <c r="D480" s="8"/>
+      <c r="E480" s="8"/>
+      <c r="F480" s="8"/>
       <c r="G480" s="3"/>
       <c r="H480" s="3"/>
       <c r="I480" s="3"/>
@@ -15700,9 +15877,9 @@
     </row>
     <row r="481" spans="3:22">
       <c r="C481" s="3"/>
-      <c r="D481" s="5"/>
-      <c r="E481" s="5"/>
-      <c r="F481" s="5"/>
+      <c r="D481" s="8"/>
+      <c r="E481" s="8"/>
+      <c r="F481" s="8"/>
       <c r="G481" s="3"/>
       <c r="H481" s="3"/>
       <c r="I481" s="3"/>
@@ -15722,9 +15899,9 @@
     </row>
     <row r="482" spans="3:22">
       <c r="C482" s="3"/>
-      <c r="D482" s="5"/>
-      <c r="E482" s="5"/>
-      <c r="F482" s="5"/>
+      <c r="D482" s="8"/>
+      <c r="E482" s="8"/>
+      <c r="F482" s="8"/>
       <c r="G482" s="3"/>
       <c r="H482" s="3"/>
       <c r="I482" s="3"/>
@@ -15744,9 +15921,9 @@
     </row>
     <row r="483" spans="3:22">
       <c r="C483" s="3"/>
-      <c r="D483" s="5"/>
-      <c r="E483" s="5"/>
-      <c r="F483" s="5"/>
+      <c r="D483" s="8"/>
+      <c r="E483" s="8"/>
+      <c r="F483" s="8"/>
       <c r="G483" s="3"/>
       <c r="H483" s="3"/>
       <c r="I483" s="3"/>
@@ -15766,9 +15943,9 @@
     </row>
     <row r="484" spans="3:22">
       <c r="C484" s="3"/>
-      <c r="D484" s="5"/>
-      <c r="E484" s="5"/>
-      <c r="F484" s="5"/>
+      <c r="D484" s="8"/>
+      <c r="E484" s="8"/>
+      <c r="F484" s="8"/>
       <c r="G484" s="3"/>
       <c r="H484" s="3"/>
       <c r="I484" s="3"/>
@@ -15788,9 +15965,9 @@
     </row>
     <row r="485" spans="3:22">
       <c r="C485" s="3"/>
-      <c r="D485" s="5"/>
-      <c r="E485" s="5"/>
-      <c r="F485" s="5"/>
+      <c r="D485" s="8"/>
+      <c r="E485" s="8"/>
+      <c r="F485" s="8"/>
       <c r="G485" s="3"/>
       <c r="H485" s="3"/>
       <c r="I485" s="3"/>
@@ -15810,9 +15987,9 @@
     </row>
     <row r="486" spans="3:22">
       <c r="C486" s="3"/>
-      <c r="D486" s="5"/>
-      <c r="E486" s="5"/>
-      <c r="F486" s="5"/>
+      <c r="D486" s="8"/>
+      <c r="E486" s="8"/>
+      <c r="F486" s="8"/>
       <c r="G486" s="3"/>
       <c r="H486" s="3"/>
       <c r="I486" s="3"/>
@@ -15832,9 +16009,9 @@
     </row>
     <row r="487" spans="3:22">
       <c r="C487" s="3"/>
-      <c r="D487" s="5"/>
-      <c r="E487" s="5"/>
-      <c r="F487" s="5"/>
+      <c r="D487" s="8"/>
+      <c r="E487" s="8"/>
+      <c r="F487" s="8"/>
       <c r="G487" s="3"/>
       <c r="H487" s="3"/>
       <c r="I487" s="3"/>
@@ -15854,9 +16031,9 @@
     </row>
     <row r="488" spans="3:22">
       <c r="C488" s="3"/>
-      <c r="D488" s="5"/>
-      <c r="E488" s="5"/>
-      <c r="F488" s="5"/>
+      <c r="D488" s="8"/>
+      <c r="E488" s="8"/>
+      <c r="F488" s="8"/>
       <c r="G488" s="3"/>
       <c r="H488" s="3"/>
       <c r="I488" s="3"/>
@@ -15876,9 +16053,9 @@
     </row>
     <row r="489" spans="3:22">
       <c r="C489" s="3"/>
-      <c r="D489" s="5"/>
-      <c r="E489" s="5"/>
-      <c r="F489" s="5"/>
+      <c r="D489" s="8"/>
+      <c r="E489" s="8"/>
+      <c r="F489" s="8"/>
       <c r="G489" s="3"/>
       <c r="H489" s="3"/>
       <c r="I489" s="3"/>
@@ -15898,9 +16075,9 @@
     </row>
     <row r="490" spans="3:22">
       <c r="C490" s="3"/>
-      <c r="D490" s="5"/>
-      <c r="E490" s="5"/>
-      <c r="F490" s="5"/>
+      <c r="D490" s="8"/>
+      <c r="E490" s="8"/>
+      <c r="F490" s="8"/>
       <c r="G490" s="3"/>
       <c r="H490" s="3"/>
       <c r="I490" s="3"/>
@@ -15920,9 +16097,9 @@
     </row>
     <row r="491" spans="3:22">
       <c r="C491" s="3"/>
-      <c r="D491" s="5"/>
-      <c r="E491" s="5"/>
-      <c r="F491" s="5"/>
+      <c r="D491" s="8"/>
+      <c r="E491" s="8"/>
+      <c r="F491" s="8"/>
       <c r="G491" s="3"/>
       <c r="H491" s="3"/>
       <c r="I491" s="3"/>
@@ -15942,9 +16119,9 @@
     </row>
     <row r="492" spans="3:22">
       <c r="C492" s="3"/>
-      <c r="D492" s="5"/>
-      <c r="E492" s="5"/>
-      <c r="F492" s="5"/>
+      <c r="D492" s="8"/>
+      <c r="E492" s="8"/>
+      <c r="F492" s="8"/>
       <c r="G492" s="3"/>
       <c r="H492" s="3"/>
       <c r="I492" s="3"/>
@@ -15964,9 +16141,9 @@
     </row>
     <row r="493" spans="3:22">
       <c r="C493" s="3"/>
-      <c r="D493" s="5"/>
-      <c r="E493" s="5"/>
-      <c r="F493" s="5"/>
+      <c r="D493" s="8"/>
+      <c r="E493" s="8"/>
+      <c r="F493" s="8"/>
       <c r="G493" s="3"/>
       <c r="H493" s="3"/>
       <c r="I493" s="3"/>
@@ -15986,9 +16163,9 @@
     </row>
     <row r="494" spans="3:22">
       <c r="C494" s="3"/>
-      <c r="D494" s="5"/>
-      <c r="E494" s="5"/>
-      <c r="F494" s="5"/>
+      <c r="D494" s="8"/>
+      <c r="E494" s="8"/>
+      <c r="F494" s="8"/>
       <c r="G494" s="3"/>
       <c r="H494" s="3"/>
       <c r="I494" s="3"/>
@@ -16008,9 +16185,9 @@
     </row>
     <row r="495" spans="3:22">
       <c r="C495" s="3"/>
-      <c r="D495" s="5"/>
-      <c r="E495" s="5"/>
-      <c r="F495" s="5"/>
+      <c r="D495" s="8"/>
+      <c r="E495" s="8"/>
+      <c r="F495" s="8"/>
       <c r="G495" s="3"/>
       <c r="H495" s="3"/>
       <c r="I495" s="3"/>
@@ -16030,9 +16207,9 @@
     </row>
     <row r="496" spans="3:22">
       <c r="C496" s="3"/>
-      <c r="D496" s="5"/>
-      <c r="E496" s="5"/>
-      <c r="F496" s="5"/>
+      <c r="D496" s="8"/>
+      <c r="E496" s="8"/>
+      <c r="F496" s="8"/>
       <c r="G496" s="3"/>
       <c r="H496" s="3"/>
       <c r="I496" s="3"/>
@@ -16052,9 +16229,9 @@
     </row>
     <row r="497" spans="3:22">
       <c r="C497" s="3"/>
-      <c r="D497" s="5"/>
-      <c r="E497" s="5"/>
-      <c r="F497" s="5"/>
+      <c r="D497" s="8"/>
+      <c r="E497" s="8"/>
+      <c r="F497" s="8"/>
       <c r="G497" s="3"/>
       <c r="H497" s="3"/>
       <c r="I497" s="3"/>
@@ -16074,9 +16251,9 @@
     </row>
     <row r="498" spans="3:22">
       <c r="C498" s="3"/>
-      <c r="D498" s="5"/>
-      <c r="E498" s="5"/>
-      <c r="F498" s="5"/>
+      <c r="D498" s="8"/>
+      <c r="E498" s="8"/>
+      <c r="F498" s="8"/>
       <c r="G498" s="3"/>
       <c r="H498" s="3"/>
       <c r="I498" s="3"/>
@@ -16096,9 +16273,9 @@
     </row>
     <row r="499" spans="3:22">
       <c r="C499" s="3"/>
-      <c r="D499" s="5"/>
-      <c r="E499" s="5"/>
-      <c r="F499" s="5"/>
+      <c r="D499" s="8"/>
+      <c r="E499" s="8"/>
+      <c r="F499" s="8"/>
       <c r="G499" s="3"/>
       <c r="H499" s="3"/>
       <c r="I499" s="3"/>
@@ -16118,9 +16295,9 @@
     </row>
     <row r="500" spans="3:22">
       <c r="C500" s="3"/>
-      <c r="D500" s="5"/>
-      <c r="E500" s="5"/>
-      <c r="F500" s="5"/>
+      <c r="D500" s="8"/>
+      <c r="E500" s="8"/>
+      <c r="F500" s="8"/>
       <c r="G500" s="3"/>
       <c r="H500" s="3"/>
       <c r="I500" s="3"/>
@@ -16140,9 +16317,9 @@
     </row>
     <row r="501" spans="3:22">
       <c r="C501" s="3"/>
-      <c r="D501" s="5"/>
-      <c r="E501" s="5"/>
-      <c r="F501" s="5"/>
+      <c r="D501" s="8"/>
+      <c r="E501" s="8"/>
+      <c r="F501" s="8"/>
       <c r="G501" s="3"/>
       <c r="H501" s="3"/>
       <c r="I501" s="3"/>
@@ -16162,9 +16339,9 @@
     </row>
     <row r="502" spans="3:22">
       <c r="C502" s="3"/>
-      <c r="D502" s="5"/>
-      <c r="E502" s="5"/>
-      <c r="F502" s="5"/>
+      <c r="D502" s="8"/>
+      <c r="E502" s="8"/>
+      <c r="F502" s="8"/>
       <c r="G502" s="3"/>
       <c r="H502" s="3"/>
       <c r="I502" s="3"/>
@@ -16184,9 +16361,9 @@
     </row>
     <row r="503" spans="3:22">
       <c r="C503" s="3"/>
-      <c r="D503" s="5"/>
-      <c r="E503" s="5"/>
-      <c r="F503" s="5"/>
+      <c r="D503" s="8"/>
+      <c r="E503" s="8"/>
+      <c r="F503" s="8"/>
       <c r="G503" s="3"/>
       <c r="H503" s="3"/>
       <c r="I503" s="3"/>
@@ -16206,9 +16383,9 @@
     </row>
     <row r="504" spans="3:22">
       <c r="C504" s="3"/>
-      <c r="D504" s="5"/>
-      <c r="E504" s="5"/>
-      <c r="F504" s="5"/>
+      <c r="D504" s="8"/>
+      <c r="E504" s="8"/>
+      <c r="F504" s="8"/>
       <c r="G504" s="3"/>
       <c r="H504" s="3"/>
       <c r="I504" s="3"/>
@@ -16228,9 +16405,9 @@
     </row>
     <row r="505" spans="3:22">
       <c r="C505" s="3"/>
-      <c r="D505" s="5"/>
-      <c r="E505" s="5"/>
-      <c r="F505" s="5"/>
+      <c r="D505" s="8"/>
+      <c r="E505" s="8"/>
+      <c r="F505" s="8"/>
       <c r="G505" s="3"/>
       <c r="H505" s="3"/>
       <c r="I505" s="3"/>
@@ -16250,9 +16427,9 @@
     </row>
     <row r="506" spans="3:22">
       <c r="C506" s="3"/>
-      <c r="D506" s="5"/>
-      <c r="E506" s="5"/>
-      <c r="F506" s="5"/>
+      <c r="D506" s="8"/>
+      <c r="E506" s="8"/>
+      <c r="F506" s="8"/>
       <c r="G506" s="3"/>
       <c r="H506" s="3"/>
       <c r="I506" s="3"/>
@@ -16272,9 +16449,9 @@
     </row>
     <row r="507" spans="3:22">
       <c r="C507" s="3"/>
-      <c r="D507" s="5"/>
-      <c r="E507" s="5"/>
-      <c r="F507" s="5"/>
+      <c r="D507" s="8"/>
+      <c r="E507" s="8"/>
+      <c r="F507" s="8"/>
       <c r="G507" s="3"/>
       <c r="H507" s="3"/>
       <c r="I507" s="3"/>
@@ -16294,9 +16471,9 @@
     </row>
     <row r="508" spans="3:22">
       <c r="C508" s="3"/>
-      <c r="D508" s="5"/>
-      <c r="E508" s="5"/>
-      <c r="F508" s="5"/>
+      <c r="D508" s="8"/>
+      <c r="E508" s="8"/>
+      <c r="F508" s="8"/>
       <c r="G508" s="3"/>
       <c r="H508" s="3"/>
       <c r="I508" s="3"/>
@@ -16316,9 +16493,9 @@
     </row>
     <row r="509" spans="3:22">
       <c r="C509" s="3"/>
-      <c r="D509" s="5"/>
-      <c r="E509" s="5"/>
-      <c r="F509" s="5"/>
+      <c r="D509" s="8"/>
+      <c r="E509" s="8"/>
+      <c r="F509" s="8"/>
       <c r="G509" s="3"/>
       <c r="H509" s="3"/>
       <c r="I509" s="3"/>
@@ -16338,9 +16515,9 @@
     </row>
     <row r="510" spans="3:22">
       <c r="C510" s="3"/>
-      <c r="D510" s="5"/>
-      <c r="E510" s="5"/>
-      <c r="F510" s="5"/>
+      <c r="D510" s="8"/>
+      <c r="E510" s="8"/>
+      <c r="F510" s="8"/>
       <c r="G510" s="3"/>
       <c r="H510" s="3"/>
       <c r="I510" s="3"/>
@@ -16360,9 +16537,9 @@
     </row>
     <row r="511" spans="3:22">
       <c r="C511" s="3"/>
-      <c r="D511" s="5"/>
-      <c r="E511" s="5"/>
-      <c r="F511" s="5"/>
+      <c r="D511" s="8"/>
+      <c r="E511" s="8"/>
+      <c r="F511" s="8"/>
       <c r="G511" s="3"/>
       <c r="H511" s="3"/>
       <c r="I511" s="3"/>
@@ -16382,9 +16559,9 @@
     </row>
     <row r="512" spans="3:22">
       <c r="C512" s="3"/>
-      <c r="D512" s="5"/>
-      <c r="E512" s="5"/>
-      <c r="F512" s="5"/>
+      <c r="D512" s="8"/>
+      <c r="E512" s="8"/>
+      <c r="F512" s="8"/>
       <c r="G512" s="3"/>
       <c r="H512" s="3"/>
       <c r="I512" s="3"/>
@@ -16404,9 +16581,9 @@
     </row>
     <row r="513" spans="3:22">
       <c r="C513" s="3"/>
-      <c r="D513" s="5"/>
-      <c r="E513" s="5"/>
-      <c r="F513" s="5"/>
+      <c r="D513" s="8"/>
+      <c r="E513" s="8"/>
+      <c r="F513" s="8"/>
       <c r="G513" s="3"/>
       <c r="H513" s="3"/>
       <c r="I513" s="3"/>
@@ -16426,9 +16603,9 @@
     </row>
     <row r="514" spans="3:22">
       <c r="C514" s="3"/>
-      <c r="D514" s="5"/>
-      <c r="E514" s="5"/>
-      <c r="F514" s="5"/>
+      <c r="D514" s="8"/>
+      <c r="E514" s="8"/>
+      <c r="F514" s="8"/>
       <c r="G514" s="3"/>
       <c r="H514" s="3"/>
       <c r="I514" s="3"/>
@@ -16448,9 +16625,9 @@
     </row>
     <row r="515" spans="3:22">
       <c r="C515" s="3"/>
-      <c r="D515" s="5"/>
-      <c r="E515" s="5"/>
-      <c r="F515" s="5"/>
+      <c r="D515" s="8"/>
+      <c r="E515" s="8"/>
+      <c r="F515" s="8"/>
       <c r="G515" s="3"/>
       <c r="H515" s="3"/>
       <c r="I515" s="3"/>
@@ -16470,9 +16647,9 @@
     </row>
     <row r="516" spans="3:22">
       <c r="C516" s="3"/>
-      <c r="D516" s="5"/>
-      <c r="E516" s="5"/>
-      <c r="F516" s="5"/>
+      <c r="D516" s="8"/>
+      <c r="E516" s="8"/>
+      <c r="F516" s="8"/>
       <c r="G516" s="3"/>
       <c r="H516" s="3"/>
       <c r="I516" s="3"/>
@@ -16492,9 +16669,9 @@
     </row>
     <row r="517" spans="3:22">
       <c r="C517" s="3"/>
-      <c r="D517" s="5"/>
-      <c r="E517" s="5"/>
-      <c r="F517" s="5"/>
+      <c r="D517" s="8"/>
+      <c r="E517" s="8"/>
+      <c r="F517" s="8"/>
       <c r="G517" s="3"/>
       <c r="H517" s="3"/>
       <c r="I517" s="3"/>
@@ -16514,9 +16691,9 @@
     </row>
     <row r="518" spans="3:22">
       <c r="C518" s="3"/>
-      <c r="D518" s="5"/>
-      <c r="E518" s="5"/>
-      <c r="F518" s="5"/>
+      <c r="D518" s="8"/>
+      <c r="E518" s="8"/>
+      <c r="F518" s="8"/>
       <c r="G518" s="3"/>
       <c r="H518" s="3"/>
       <c r="I518" s="3"/>
@@ -16536,9 +16713,9 @@
     </row>
     <row r="519" spans="3:22">
       <c r="C519" s="3"/>
-      <c r="D519" s="5"/>
-      <c r="E519" s="5"/>
-      <c r="F519" s="5"/>
+      <c r="D519" s="8"/>
+      <c r="E519" s="8"/>
+      <c r="F519" s="8"/>
       <c r="G519" s="3"/>
       <c r="H519" s="3"/>
       <c r="I519" s="3"/>
@@ -16558,9 +16735,9 @@
     </row>
     <row r="520" spans="3:22">
       <c r="C520" s="3"/>
-      <c r="D520" s="5"/>
-      <c r="E520" s="5"/>
-      <c r="F520" s="5"/>
+      <c r="D520" s="8"/>
+      <c r="E520" s="8"/>
+      <c r="F520" s="8"/>
       <c r="G520" s="3"/>
       <c r="H520" s="3"/>
       <c r="I520" s="3"/>
@@ -16580,9 +16757,9 @@
     </row>
     <row r="521" spans="3:22">
       <c r="C521" s="3"/>
-      <c r="D521" s="5"/>
-      <c r="E521" s="5"/>
-      <c r="F521" s="5"/>
+      <c r="D521" s="8"/>
+      <c r="E521" s="8"/>
+      <c r="F521" s="8"/>
       <c r="G521" s="3"/>
       <c r="H521" s="3"/>
       <c r="I521" s="3"/>
@@ -16602,9 +16779,9 @@
     </row>
     <row r="522" spans="3:22">
       <c r="C522" s="3"/>
-      <c r="D522" s="5"/>
-      <c r="E522" s="5"/>
-      <c r="F522" s="5"/>
+      <c r="D522" s="8"/>
+      <c r="E522" s="8"/>
+      <c r="F522" s="8"/>
       <c r="G522" s="3"/>
       <c r="H522" s="3"/>
       <c r="I522" s="3"/>
@@ -16624,9 +16801,9 @@
     </row>
     <row r="523" spans="3:22">
       <c r="C523" s="3"/>
-      <c r="D523" s="5"/>
-      <c r="E523" s="5"/>
-      <c r="F523" s="5"/>
+      <c r="D523" s="8"/>
+      <c r="E523" s="8"/>
+      <c r="F523" s="8"/>
       <c r="G523" s="3"/>
       <c r="H523" s="3"/>
       <c r="I523" s="3"/>
@@ -16646,9 +16823,9 @@
     </row>
     <row r="524" spans="3:22">
       <c r="C524" s="3"/>
-      <c r="D524" s="5"/>
-      <c r="E524" s="5"/>
-      <c r="F524" s="5"/>
+      <c r="D524" s="8"/>
+      <c r="E524" s="8"/>
+      <c r="F524" s="8"/>
       <c r="G524" s="3"/>
       <c r="H524" s="3"/>
       <c r="I524" s="3"/>
@@ -16668,9 +16845,9 @@
     </row>
     <row r="525" spans="3:22">
       <c r="C525" s="3"/>
-      <c r="D525" s="5"/>
-      <c r="E525" s="5"/>
-      <c r="F525" s="5"/>
+      <c r="D525" s="8"/>
+      <c r="E525" s="8"/>
+      <c r="F525" s="8"/>
       <c r="G525" s="3"/>
       <c r="H525" s="3"/>
       <c r="I525" s="3"/>
@@ -16690,9 +16867,9 @@
     </row>
     <row r="526" spans="3:22">
       <c r="C526" s="3"/>
-      <c r="D526" s="5"/>
-      <c r="E526" s="5"/>
-      <c r="F526" s="5"/>
+      <c r="D526" s="8"/>
+      <c r="E526" s="8"/>
+      <c r="F526" s="8"/>
       <c r="G526" s="3"/>
       <c r="H526" s="3"/>
       <c r="I526" s="3"/>
@@ -16712,9 +16889,9 @@
     </row>
     <row r="527" spans="3:22">
       <c r="C527" s="3"/>
-      <c r="D527" s="5"/>
-      <c r="E527" s="5"/>
-      <c r="F527" s="5"/>
+      <c r="D527" s="8"/>
+      <c r="E527" s="8"/>
+      <c r="F527" s="8"/>
       <c r="G527" s="3"/>
       <c r="H527" s="3"/>
       <c r="I527" s="3"/>
@@ -16734,9 +16911,9 @@
     </row>
     <row r="528" spans="3:22">
       <c r="C528" s="3"/>
-      <c r="D528" s="5"/>
-      <c r="E528" s="5"/>
-      <c r="F528" s="5"/>
+      <c r="D528" s="8"/>
+      <c r="E528" s="8"/>
+      <c r="F528" s="8"/>
       <c r="G528" s="3"/>
       <c r="H528" s="3"/>
       <c r="I528" s="3"/>
@@ -16756,9 +16933,9 @@
     </row>
     <row r="529" spans="3:22">
       <c r="C529" s="3"/>
-      <c r="D529" s="5"/>
-      <c r="E529" s="5"/>
-      <c r="F529" s="5"/>
+      <c r="D529" s="8"/>
+      <c r="E529" s="8"/>
+      <c r="F529" s="8"/>
       <c r="G529" s="3"/>
       <c r="H529" s="3"/>
       <c r="I529" s="3"/>
@@ -16778,9 +16955,9 @@
     </row>
     <row r="530" spans="3:22">
       <c r="C530" s="3"/>
-      <c r="D530" s="5"/>
-      <c r="E530" s="5"/>
-      <c r="F530" s="5"/>
+      <c r="D530" s="8"/>
+      <c r="E530" s="8"/>
+      <c r="F530" s="8"/>
       <c r="G530" s="3"/>
       <c r="H530" s="3"/>
       <c r="I530" s="3"/>
@@ -16800,9 +16977,9 @@
     </row>
     <row r="531" spans="3:22">
       <c r="C531" s="3"/>
-      <c r="D531" s="5"/>
-      <c r="E531" s="5"/>
-      <c r="F531" s="5"/>
+      <c r="D531" s="8"/>
+      <c r="E531" s="8"/>
+      <c r="F531" s="8"/>
       <c r="G531" s="3"/>
       <c r="H531" s="3"/>
       <c r="I531" s="3"/>
@@ -16822,9 +16999,9 @@
     </row>
     <row r="532" spans="3:22">
       <c r="C532" s="3"/>
-      <c r="D532" s="5"/>
-      <c r="E532" s="5"/>
-      <c r="F532" s="5"/>
+      <c r="D532" s="8"/>
+      <c r="E532" s="8"/>
+      <c r="F532" s="8"/>
       <c r="G532" s="3"/>
       <c r="H532" s="3"/>
       <c r="I532" s="3"/>
@@ -16844,9 +17021,9 @@
     </row>
     <row r="533" spans="3:22">
       <c r="C533" s="3"/>
-      <c r="D533" s="5"/>
-      <c r="E533" s="5"/>
-      <c r="F533" s="5"/>
+      <c r="D533" s="8"/>
+      <c r="E533" s="8"/>
+      <c r="F533" s="8"/>
       <c r="G533" s="3"/>
       <c r="H533" s="3"/>
       <c r="I533" s="3"/>
@@ -16866,9 +17043,9 @@
     </row>
     <row r="534" spans="3:22">
       <c r="C534" s="3"/>
-      <c r="D534" s="5"/>
-      <c r="E534" s="5"/>
-      <c r="F534" s="5"/>
+      <c r="D534" s="8"/>
+      <c r="E534" s="8"/>
+      <c r="F534" s="8"/>
       <c r="G534" s="3"/>
       <c r="H534" s="3"/>
       <c r="I534" s="3"/>
@@ -16888,9 +17065,9 @@
     </row>
     <row r="535" spans="3:22">
       <c r="C535" s="3"/>
-      <c r="D535" s="5"/>
-      <c r="E535" s="5"/>
-      <c r="F535" s="5"/>
+      <c r="D535" s="8"/>
+      <c r="E535" s="8"/>
+      <c r="F535" s="8"/>
       <c r="G535" s="3"/>
       <c r="H535" s="3"/>
       <c r="I535" s="3"/>
@@ -16910,9 +17087,9 @@
     </row>
     <row r="536" spans="3:22">
       <c r="C536" s="3"/>
-      <c r="D536" s="5"/>
-      <c r="E536" s="5"/>
-      <c r="F536" s="5"/>
+      <c r="D536" s="8"/>
+      <c r="E536" s="8"/>
+      <c r="F536" s="8"/>
       <c r="G536" s="3"/>
       <c r="H536" s="3"/>
       <c r="I536" s="3"/>
@@ -16932,9 +17109,9 @@
     </row>
     <row r="537" spans="3:22">
       <c r="C537" s="3"/>
-      <c r="D537" s="5"/>
-      <c r="E537" s="5"/>
-      <c r="F537" s="5"/>
+      <c r="D537" s="8"/>
+      <c r="E537" s="8"/>
+      <c r="F537" s="8"/>
       <c r="G537" s="3"/>
       <c r="H537" s="3"/>
       <c r="I537" s="3"/>
@@ -16954,9 +17131,9 @@
     </row>
     <row r="538" spans="3:22">
       <c r="C538" s="3"/>
-      <c r="D538" s="5"/>
-      <c r="E538" s="5"/>
-      <c r="F538" s="5"/>
+      <c r="D538" s="8"/>
+      <c r="E538" s="8"/>
+      <c r="F538" s="8"/>
       <c r="G538" s="3"/>
       <c r="H538" s="3"/>
       <c r="I538" s="3"/>
@@ -16976,9 +17153,9 @@
     </row>
     <row r="539" spans="3:22">
       <c r="C539" s="3"/>
-      <c r="D539" s="5"/>
-      <c r="E539" s="5"/>
-      <c r="F539" s="5"/>
+      <c r="D539" s="8"/>
+      <c r="E539" s="8"/>
+      <c r="F539" s="8"/>
       <c r="G539" s="3"/>
       <c r="H539" s="3"/>
       <c r="I539" s="3"/>
@@ -16998,9 +17175,9 @@
     </row>
     <row r="540" spans="3:22">
       <c r="C540" s="3"/>
-      <c r="D540" s="5"/>
-      <c r="E540" s="5"/>
-      <c r="F540" s="5"/>
+      <c r="D540" s="8"/>
+      <c r="E540" s="8"/>
+      <c r="F540" s="8"/>
       <c r="G540" s="3"/>
       <c r="H540" s="3"/>
       <c r="I540" s="3"/>
@@ -17020,9 +17197,9 @@
     </row>
     <row r="541" spans="3:22">
       <c r="C541" s="3"/>
-      <c r="D541" s="5"/>
-      <c r="E541" s="5"/>
-      <c r="F541" s="5"/>
+      <c r="D541" s="8"/>
+      <c r="E541" s="8"/>
+      <c r="F541" s="8"/>
       <c r="G541" s="3"/>
       <c r="H541" s="3"/>
       <c r="I541" s="3"/>
@@ -17042,9 +17219,9 @@
     </row>
     <row r="542" spans="3:22">
       <c r="C542" s="3"/>
-      <c r="D542" s="5"/>
-      <c r="E542" s="5"/>
-      <c r="F542" s="5"/>
+      <c r="D542" s="8"/>
+      <c r="E542" s="8"/>
+      <c r="F542" s="8"/>
       <c r="G542" s="3"/>
       <c r="H542" s="3"/>
       <c r="I542" s="3"/>
@@ -17064,9 +17241,9 @@
     </row>
     <row r="543" spans="3:22">
       <c r="C543" s="3"/>
-      <c r="D543" s="5"/>
-      <c r="E543" s="5"/>
-      <c r="F543" s="5"/>
+      <c r="D543" s="8"/>
+      <c r="E543" s="8"/>
+      <c r="F543" s="8"/>
       <c r="G543" s="3"/>
       <c r="H543" s="3"/>
       <c r="I543" s="3"/>
@@ -17086,9 +17263,9 @@
     </row>
     <row r="544" spans="3:22">
       <c r="C544" s="3"/>
-      <c r="D544" s="5"/>
-      <c r="E544" s="5"/>
-      <c r="F544" s="5"/>
+      <c r="D544" s="8"/>
+      <c r="E544" s="8"/>
+      <c r="F544" s="8"/>
       <c r="G544" s="3"/>
       <c r="H544" s="3"/>
       <c r="I544" s="3"/>
@@ -17108,9 +17285,9 @@
     </row>
     <row r="545" spans="3:22">
       <c r="C545" s="3"/>
-      <c r="D545" s="5"/>
-      <c r="E545" s="5"/>
-      <c r="F545" s="5"/>
+      <c r="D545" s="8"/>
+      <c r="E545" s="8"/>
+      <c r="F545" s="8"/>
       <c r="G545" s="3"/>
       <c r="H545" s="3"/>
       <c r="I545" s="3"/>
@@ -17130,9 +17307,9 @@
     </row>
     <row r="546" spans="3:22">
       <c r="C546" s="3"/>
-      <c r="D546" s="5"/>
-      <c r="E546" s="5"/>
-      <c r="F546" s="5"/>
+      <c r="D546" s="8"/>
+      <c r="E546" s="8"/>
+      <c r="F546" s="8"/>
       <c r="G546" s="3"/>
       <c r="H546" s="3"/>
       <c r="I546" s="3"/>
@@ -17152,9 +17329,9 @@
     </row>
     <row r="547" spans="3:22">
       <c r="C547" s="3"/>
-      <c r="D547" s="5"/>
-      <c r="E547" s="5"/>
-      <c r="F547" s="5"/>
+      <c r="D547" s="8"/>
+      <c r="E547" s="8"/>
+      <c r="F547" s="8"/>
       <c r="G547" s="3"/>
       <c r="H547" s="3"/>
       <c r="I547" s="3"/>
@@ -17174,9 +17351,9 @@
     </row>
     <row r="548" spans="3:22">
       <c r="C548" s="3"/>
-      <c r="D548" s="5"/>
-      <c r="E548" s="5"/>
-      <c r="F548" s="5"/>
+      <c r="D548" s="8"/>
+      <c r="E548" s="8"/>
+      <c r="F548" s="8"/>
       <c r="G548" s="3"/>
       <c r="H548" s="3"/>
       <c r="I548" s="3"/>
@@ -17196,9 +17373,9 @@
     </row>
     <row r="549" spans="3:22">
       <c r="C549" s="3"/>
-      <c r="D549" s="5"/>
-      <c r="E549" s="5"/>
-      <c r="F549" s="5"/>
+      <c r="D549" s="8"/>
+      <c r="E549" s="8"/>
+      <c r="F549" s="8"/>
       <c r="G549" s="3"/>
       <c r="H549" s="3"/>
       <c r="I549" s="3"/>
@@ -17218,9 +17395,9 @@
     </row>
     <row r="550" spans="3:22">
       <c r="C550" s="3"/>
-      <c r="D550" s="5"/>
-      <c r="E550" s="5"/>
-      <c r="F550" s="5"/>
+      <c r="D550" s="8"/>
+      <c r="E550" s="8"/>
+      <c r="F550" s="8"/>
       <c r="G550" s="3"/>
       <c r="H550" s="3"/>
       <c r="I550" s="3"/>
@@ -17240,9 +17417,9 @@
     </row>
     <row r="551" spans="3:22">
       <c r="C551" s="3"/>
-      <c r="D551" s="5"/>
-      <c r="E551" s="5"/>
-      <c r="F551" s="5"/>
+      <c r="D551" s="8"/>
+      <c r="E551" s="8"/>
+      <c r="F551" s="8"/>
       <c r="G551" s="3"/>
       <c r="H551" s="3"/>
       <c r="I551" s="3"/>
@@ -17262,9 +17439,9 @@
     </row>
     <row r="552" spans="3:22">
       <c r="C552" s="3"/>
-      <c r="D552" s="5"/>
-      <c r="E552" s="5"/>
-      <c r="F552" s="5"/>
+      <c r="D552" s="8"/>
+      <c r="E552" s="8"/>
+      <c r="F552" s="8"/>
       <c r="G552" s="3"/>
       <c r="H552" s="3"/>
       <c r="I552" s="3"/>
@@ -17284,9 +17461,9 @@
     </row>
     <row r="553" spans="3:22">
       <c r="C553" s="3"/>
-      <c r="D553" s="5"/>
-      <c r="E553" s="5"/>
-      <c r="F553" s="5"/>
+      <c r="D553" s="8"/>
+      <c r="E553" s="8"/>
+      <c r="F553" s="8"/>
       <c r="G553" s="3"/>
       <c r="H553" s="3"/>
       <c r="I553" s="3"/>
@@ -17306,9 +17483,9 @@
     </row>
     <row r="554" spans="3:22">
       <c r="C554" s="3"/>
-      <c r="D554" s="5"/>
-      <c r="E554" s="5"/>
-      <c r="F554" s="5"/>
+      <c r="D554" s="8"/>
+      <c r="E554" s="8"/>
+      <c r="F554" s="8"/>
       <c r="G554" s="3"/>
       <c r="H554" s="3"/>
       <c r="I554" s="3"/>
@@ -17328,9 +17505,9 @@
     </row>
     <row r="555" spans="3:22">
       <c r="C555" s="3"/>
-      <c r="D555" s="5"/>
-      <c r="E555" s="5"/>
-      <c r="F555" s="5"/>
+      <c r="D555" s="8"/>
+      <c r="E555" s="8"/>
+      <c r="F555" s="8"/>
       <c r="G555" s="3"/>
       <c r="H555" s="3"/>
       <c r="I555" s="3"/>
@@ -17350,9 +17527,9 @@
     </row>
     <row r="556" spans="3:22">
       <c r="C556" s="3"/>
-      <c r="D556" s="5"/>
-      <c r="E556" s="5"/>
-      <c r="F556" s="5"/>
+      <c r="D556" s="8"/>
+      <c r="E556" s="8"/>
+      <c r="F556" s="8"/>
       <c r="G556" s="3"/>
       <c r="H556" s="3"/>
       <c r="I556" s="3"/>
@@ -17372,9 +17549,9 @@
     </row>
     <row r="557" spans="3:22">
       <c r="C557" s="3"/>
-      <c r="D557" s="5"/>
-      <c r="E557" s="5"/>
-      <c r="F557" s="5"/>
+      <c r="D557" s="8"/>
+      <c r="E557" s="8"/>
+      <c r="F557" s="8"/>
       <c r="G557" s="3"/>
       <c r="H557" s="3"/>
       <c r="I557" s="3"/>
@@ -17394,9 +17571,9 @@
     </row>
     <row r="558" spans="3:22">
       <c r="C558" s="3"/>
-      <c r="D558" s="5"/>
-      <c r="E558" s="5"/>
-      <c r="F558" s="5"/>
+      <c r="D558" s="8"/>
+      <c r="E558" s="8"/>
+      <c r="F558" s="8"/>
       <c r="G558" s="3"/>
       <c r="H558" s="3"/>
       <c r="I558" s="3"/>
@@ -17416,9 +17593,9 @@
     </row>
     <row r="559" spans="3:22">
       <c r="C559" s="3"/>
-      <c r="D559" s="5"/>
-      <c r="E559" s="5"/>
-      <c r="F559" s="5"/>
+      <c r="D559" s="8"/>
+      <c r="E559" s="8"/>
+      <c r="F559" s="8"/>
       <c r="G559" s="3"/>
       <c r="H559" s="3"/>
       <c r="I559" s="3"/>
@@ -17438,9 +17615,9 @@
     </row>
     <row r="560" spans="3:22">
       <c r="C560" s="3"/>
-      <c r="D560" s="5"/>
-      <c r="E560" s="5"/>
-      <c r="F560" s="5"/>
+      <c r="D560" s="8"/>
+      <c r="E560" s="8"/>
+      <c r="F560" s="8"/>
       <c r="G560" s="3"/>
       <c r="H560" s="3"/>
       <c r="I560" s="3"/>
@@ -17460,9 +17637,9 @@
     </row>
     <row r="561" spans="3:22">
       <c r="C561" s="3"/>
-      <c r="D561" s="5"/>
-      <c r="E561" s="5"/>
-      <c r="F561" s="5"/>
+      <c r="D561" s="8"/>
+      <c r="E561" s="8"/>
+      <c r="F561" s="8"/>
       <c r="G561" s="3"/>
       <c r="H561" s="3"/>
       <c r="I561" s="3"/>
@@ -17482,9 +17659,9 @@
     </row>
     <row r="562" spans="3:22">
       <c r="C562" s="3"/>
-      <c r="D562" s="5"/>
-      <c r="E562" s="5"/>
-      <c r="F562" s="5"/>
+      <c r="D562" s="8"/>
+      <c r="E562" s="8"/>
+      <c r="F562" s="8"/>
       <c r="G562" s="3"/>
       <c r="H562" s="3"/>
       <c r="I562" s="3"/>
@@ -17504,9 +17681,9 @@
     </row>
     <row r="563" spans="3:22">
       <c r="C563" s="3"/>
-      <c r="D563" s="5"/>
-      <c r="E563" s="5"/>
-      <c r="F563" s="5"/>
+      <c r="D563" s="8"/>
+      <c r="E563" s="8"/>
+      <c r="F563" s="8"/>
       <c r="G563" s="3"/>
       <c r="H563" s="3"/>
       <c r="I563" s="3"/>
@@ -17526,9 +17703,9 @@
     </row>
     <row r="564" spans="3:22">
       <c r="C564" s="3"/>
-      <c r="D564" s="5"/>
-      <c r="E564" s="5"/>
-      <c r="F564" s="5"/>
+      <c r="D564" s="8"/>
+      <c r="E564" s="8"/>
+      <c r="F564" s="8"/>
       <c r="G564" s="3"/>
       <c r="H564" s="3"/>
       <c r="I564" s="3"/>
@@ -17548,9 +17725,9 @@
     </row>
     <row r="565" spans="3:22">
       <c r="C565" s="3"/>
-      <c r="D565" s="5"/>
-      <c r="E565" s="5"/>
-      <c r="F565" s="5"/>
+      <c r="D565" s="8"/>
+      <c r="E565" s="8"/>
+      <c r="F565" s="8"/>
       <c r="G565" s="3"/>
       <c r="H565" s="3"/>
       <c r="I565" s="3"/>
@@ -17570,9 +17747,9 @@
     </row>
     <row r="566" spans="3:22">
       <c r="C566" s="3"/>
-      <c r="D566" s="5"/>
-      <c r="E566" s="5"/>
-      <c r="F566" s="5"/>
+      <c r="D566" s="8"/>
+      <c r="E566" s="8"/>
+      <c r="F566" s="8"/>
       <c r="G566" s="3"/>
       <c r="H566" s="3"/>
       <c r="I566" s="3"/>
@@ -17592,9 +17769,9 @@
     </row>
     <row r="567" spans="3:22">
       <c r="C567" s="3"/>
-      <c r="D567" s="5"/>
-      <c r="E567" s="5"/>
-      <c r="F567" s="5"/>
+      <c r="D567" s="8"/>
+      <c r="E567" s="8"/>
+      <c r="F567" s="8"/>
       <c r="G567" s="3"/>
       <c r="H567" s="3"/>
       <c r="I567" s="3"/>
@@ -17614,9 +17791,9 @@
     </row>
     <row r="568" spans="3:22">
       <c r="C568" s="3"/>
-      <c r="D568" s="5"/>
-      <c r="E568" s="5"/>
-      <c r="F568" s="5"/>
+      <c r="D568" s="8"/>
+      <c r="E568" s="8"/>
+      <c r="F568" s="8"/>
       <c r="G568" s="3"/>
       <c r="H568" s="3"/>
       <c r="I568" s="3"/>
@@ -17636,9 +17813,9 @@
     </row>
     <row r="569" spans="3:22">
       <c r="C569" s="3"/>
-      <c r="D569" s="5"/>
-      <c r="E569" s="5"/>
-      <c r="F569" s="5"/>
+      <c r="D569" s="8"/>
+      <c r="E569" s="8"/>
+      <c r="F569" s="8"/>
       <c r="G569" s="3"/>
       <c r="H569" s="3"/>
       <c r="I569" s="3"/>
@@ -17658,9 +17835,9 @@
     </row>
     <row r="570" spans="3:22">
       <c r="C570" s="3"/>
-      <c r="D570" s="5"/>
-      <c r="E570" s="5"/>
-      <c r="F570" s="5"/>
+      <c r="D570" s="8"/>
+      <c r="E570" s="8"/>
+      <c r="F570" s="8"/>
       <c r="G570" s="3"/>
       <c r="H570" s="3"/>
       <c r="I570" s="3"/>
@@ -17680,9 +17857,9 @@
     </row>
     <row r="571" spans="3:22">
       <c r="C571" s="3"/>
-      <c r="D571" s="5"/>
-      <c r="E571" s="5"/>
-      <c r="F571" s="5"/>
+      <c r="D571" s="8"/>
+      <c r="E571" s="8"/>
+      <c r="F571" s="8"/>
       <c r="G571" s="3"/>
       <c r="H571" s="3"/>
       <c r="I571" s="3"/>
@@ -17702,9 +17879,9 @@
     </row>
     <row r="572" spans="3:22">
       <c r="C572" s="3"/>
-      <c r="D572" s="5"/>
-      <c r="E572" s="5"/>
-      <c r="F572" s="5"/>
+      <c r="D572" s="8"/>
+      <c r="E572" s="8"/>
+      <c r="F572" s="8"/>
       <c r="G572" s="3"/>
       <c r="H572" s="3"/>
       <c r="I572" s="3"/>
@@ -17724,9 +17901,9 @@
     </row>
     <row r="573" spans="3:22">
       <c r="C573" s="3"/>
-      <c r="D573" s="5"/>
-      <c r="E573" s="5"/>
-      <c r="F573" s="5"/>
+      <c r="D573" s="8"/>
+      <c r="E573" s="8"/>
+      <c r="F573" s="8"/>
       <c r="G573" s="3"/>
       <c r="H573" s="3"/>
       <c r="I573" s="3"/>
@@ -17746,9 +17923,9 @@
     </row>
     <row r="574" spans="3:22">
       <c r="C574" s="3"/>
-      <c r="D574" s="5"/>
-      <c r="E574" s="5"/>
-      <c r="F574" s="5"/>
+      <c r="D574" s="8"/>
+      <c r="E574" s="8"/>
+      <c r="F574" s="8"/>
       <c r="G574" s="3"/>
       <c r="H574" s="3"/>
       <c r="I574" s="3"/>

--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21000" windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="616">
   <si>
     <t>int</t>
   </si>
@@ -1837,6 +1837,49 @@
   </si>
   <si>
     <t>删除成功</t>
+  </si>
+  <si>
+    <t>Text_Remaining</t>
+  </si>
+  <si>
+    <t>剩余:{0}天</t>
+  </si>
+  <si>
+    <t>Text_Vip1</t>
+  </si>
+  <si>
+    <t>广告播放失败，请重试</t>
+  </si>
+  <si>
+    <t>Text_Vip2</t>
+  </si>
+  <si>
+    <t>Vip购买</t>
+  </si>
+  <si>
+    <t>Text_Vip3</t>
+  </si>
+  <si>
+    <t>{0}天Vip
+Vip期间可免费保存所有服装</t>
+  </si>
+  <si>
+    <t>Text_Vip4</t>
+  </si>
+  <si>
+    <t>{0}派对币购买</t>
+  </si>
+  <si>
+    <t>Text_Vip5</t>
+  </si>
+  <si>
+    <t>看广告获得</t>
+  </si>
+  <si>
+    <t>Text_Vip6</t>
+  </si>
+  <si>
+    <t>购买Vip成功</t>
   </si>
 </sst>
 </file>
@@ -2502,11 +2545,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -10008,10 +10051,16 @@
       <c r="V235" s="2"/>
     </row>
     <row r="236" ht="17" customHeight="1" spans="1:22">
-      <c r="A236" s="1"/>
-      <c r="B236" s="1"/>
+      <c r="A236" s="1">
+        <v>232</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>602</v>
+      </c>
       <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
+      <c r="D236" s="2" t="s">
+        <v>603</v>
+      </c>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
@@ -10032,10 +10081,16 @@
       <c r="V236" s="2"/>
     </row>
     <row r="237" ht="17" customHeight="1" spans="1:22">
-      <c r="A237" s="1"/>
-      <c r="B237" s="1"/>
+      <c r="A237" s="1">
+        <v>233</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>604</v>
+      </c>
       <c r="C237" s="2"/>
-      <c r="D237" s="4"/>
+      <c r="D237" s="4" t="s">
+        <v>605</v>
+      </c>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
       <c r="G237" s="2"/>
@@ -10056,10 +10111,16 @@
       <c r="V237" s="2"/>
     </row>
     <row r="238" ht="18" customHeight="1" spans="1:22">
-      <c r="A238" s="1"/>
-      <c r="B238" s="1"/>
+      <c r="A238" s="1">
+        <v>234</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>606</v>
+      </c>
       <c r="C238" s="2"/>
-      <c r="D238" s="4"/>
+      <c r="D238" s="4" t="s">
+        <v>607</v>
+      </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
       <c r="G238" s="2"/>
@@ -10080,10 +10141,16 @@
       <c r="V238" s="2"/>
     </row>
     <row r="239" ht="18" customHeight="1" spans="1:22">
-      <c r="A239" s="1"/>
-      <c r="B239" s="1"/>
+      <c r="A239" s="1">
+        <v>235</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>608</v>
+      </c>
       <c r="C239" s="2"/>
-      <c r="D239" s="4"/>
+      <c r="D239" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
       <c r="G239" s="2"/>
@@ -10104,10 +10171,16 @@
       <c r="V239" s="2"/>
     </row>
     <row r="240" ht="18" customHeight="1" spans="1:22">
-      <c r="A240" s="1"/>
-      <c r="B240" s="1"/>
+      <c r="A240" s="1">
+        <v>236</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>610</v>
+      </c>
       <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
+      <c r="D240" s="2" t="s">
+        <v>611</v>
+      </c>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
@@ -10128,10 +10201,16 @@
       <c r="V240" s="2"/>
     </row>
     <row r="241" ht="18" customHeight="1" spans="1:22">
-      <c r="A241" s="1"/>
-      <c r="B241" s="1"/>
+      <c r="A241" s="1">
+        <v>237</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>612</v>
+      </c>
       <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
+      <c r="D241" s="2" t="s">
+        <v>613</v>
+      </c>
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -10152,10 +10231,16 @@
       <c r="V241" s="2"/>
     </row>
     <row r="242" ht="18" customHeight="1" spans="1:22">
-      <c r="A242" s="1"/>
-      <c r="B242" s="1"/>
+      <c r="A242" s="1">
+        <v>238</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>614</v>
+      </c>
       <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
+      <c r="D242" s="2" t="s">
+        <v>615</v>
+      </c>
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -12341,7 +12426,7 @@
       <c r="C333" s="2"/>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
-      <c r="F333" s="5"/>
+      <c r="F333" s="6"/>
       <c r="G333" s="2"/>
       <c r="H333" s="2"/>
       <c r="I333" s="2"/>
@@ -12365,7 +12450,7 @@
       <c r="C334" s="2"/>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
-      <c r="F334" s="5"/>
+      <c r="F334" s="6"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
       <c r="I334" s="2"/>
@@ -12389,7 +12474,7 @@
       <c r="C335" s="2"/>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
-      <c r="F335" s="5"/>
+      <c r="F335" s="6"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
       <c r="I335" s="2"/>
@@ -12413,7 +12498,7 @@
       <c r="C336" s="2"/>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
-      <c r="F336" s="5"/>
+      <c r="F336" s="6"/>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
       <c r="I336" s="2"/>
@@ -12437,7 +12522,7 @@
       <c r="C337" s="2"/>
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
-      <c r="F337" s="5"/>
+      <c r="F337" s="6"/>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
       <c r="I337" s="2"/>
@@ -12461,7 +12546,7 @@
       <c r="C338" s="2"/>
       <c r="D338" s="4"/>
       <c r="E338" s="4"/>
-      <c r="F338" s="5"/>
+      <c r="F338" s="6"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="2"/>
@@ -12485,7 +12570,7 @@
       <c r="C339" s="2"/>
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
-      <c r="F339" s="5"/>
+      <c r="F339" s="6"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
       <c r="I339" s="2"/>
@@ -12509,7 +12594,7 @@
       <c r="C340" s="2"/>
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
-      <c r="F340" s="5"/>
+      <c r="F340" s="6"/>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
       <c r="I340" s="2"/>
@@ -12533,7 +12618,7 @@
       <c r="C341" s="2"/>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
-      <c r="F341" s="5"/>
+      <c r="F341" s="6"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
       <c r="I341" s="2"/>
@@ -12557,7 +12642,7 @@
       <c r="C342" s="2"/>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
-      <c r="F342" s="5"/>
+      <c r="F342" s="6"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
       <c r="I342" s="2"/>
@@ -12701,7 +12786,7 @@
       <c r="C348" s="2"/>
       <c r="D348" s="4"/>
       <c r="E348" s="4"/>
-      <c r="F348" s="6"/>
+      <c r="F348" s="5"/>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
       <c r="I348" s="2"/>

--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>欢迎来到
-春日物语：露营换装派对</t>
+赛博换装闪秀派对</t>
   </si>
   <si>
     <t>Text_UpNext</t>
@@ -2895,6 +2895,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>

--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="17055" tabRatio="500"/>
+    <workbookView windowHeight="17655" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>欢迎来到
-春日物语：露营换装派对</t>
+圣诞换装派对:后室寻宝</t>
   </si>
   <si>
     <t>Text_UpNext</t>
@@ -328,7 +328,7 @@
     <t>With the guide over, start your trip to the cherry blossom town</t>
   </si>
   <si>
-    <t>引导结束，开启你的露营之旅吧</t>
+    <t>引导结束，开启你的寻宝之旅吧</t>
   </si>
   <si>
     <t>Text_Close</t>

--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>欢迎来到
-圣诞换装派对:后室寻宝</t>
+国外山海经乐园</t>
   </si>
   <si>
     <t>Text_UpNext</t>

--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="17055" tabRatio="500"/>
+    <workbookView windowHeight="17655" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>欢迎来到
-赛博换装闪秀派对</t>
+赛博姐妹换装趴</t>
   </si>
   <si>
     <t>Text_UpNext</t>
@@ -2895,13 +2895,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>

--- a/rp/Excel/Language_多语言.xlsx
+++ b/rp/Excel/Language_多语言.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="17055" tabRatio="500"/>
+    <workbookView windowWidth="30465" windowHeight="12900" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>欢迎来到
-春日物语：露营换装派对</t>
+水上心愿广场</t>
   </si>
   <si>
     <t>Text_UpNext</t>
